--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -76,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E2D9F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,9 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -127,6 +124,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2797,59 +2797,59 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>FD-STATS-005</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the WO has no adjustments</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>S4-N1</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -2911,116 +2911,116 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>FD-FIN-002</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Work Order — Financial Info card</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Verify expanding the Financial Info 'Fees &amp; Discounts' row lists each adjustment (read-only, creation order)</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>S3-R23 / S3-R24 / §5-R9</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>FD-FIN-003</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Work Order — Financial Info card</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Verify the Financial Info 'Fees &amp; Discounts' row is hidden with no adjustments and the money section is hidden without See Financial Data</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>S3-N2 / S3-N4</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -3082,59 +3082,59 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>FD-FIN-005</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Verify the sidebar card is hidden with no whole-WO adjustments and has no Add control</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>S3-R4 / S3-R10 / S3-N1</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -3652,59 +3652,59 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>FD-EDIT-003</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Verify a save failure keeps the Edit dialog open and shows the returned error</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>S2-R30</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -3823,59 +3823,59 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>FD-REMOVE-003</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Verify removing a line-level adjustment via its inline 3-dot menu</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>S3-R17 / S3-R11a</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -4849,59 +4849,59 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>FD-CUST-015</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Verify the customer Fees &amp; Discounts tab and controls are hidden without the required permissions</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED — NEEDS-ACCOUNT</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>QA (restricted-role session)</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>Restricted-role login (tech quick-login flaky on qb) or a self-service staff role-switch: Story 13 — customer F&amp;D tab per-role enforcement; needs a non-Tech role login.</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="K77" s="6" t="inlineStr">
-        <is>
-          <t>needs-account</t>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -4963,59 +4963,59 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>FD-CUST-017</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Verify add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>S9-N1</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -5647,57 +5647,57 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>FD-TMPL-012</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>Environment window — shared env: cannot empty the location's template library (real templates in use).</t>
         </is>
       </c>
-      <c r="J91" s="7" t="inlineStr">
+      <c r="J91" s="6" t="inlineStr">
         <is>
           <t>S7-R11</t>
         </is>
       </c>
-      <c r="K91" s="7" t="inlineStr">
+      <c r="K91" s="6" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
@@ -5818,59 +5818,59 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>FD-TMPL-015</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>Template admin — negative</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Verify the template save-failure toast</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>S7-R19</t>
         </is>
       </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -6274,59 +6274,59 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>FD-PROC-006</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Processing Fee — auto-apply</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>S8-R14, S7-R5</t>
         </is>
       </c>
-      <c r="K102" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -7414,627 +7414,627 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="inlineStr">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>FD-QB-001</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee +, discount −)</t>
         </is>
       </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F122" s="7" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G122" s="7" t="inlineStr">
+      <c r="G122" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H122" s="7" t="inlineStr">
+      <c r="H122" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I122" s="7" t="inlineStr">
+      <c r="I122" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J122" s="7" t="inlineStr">
+      <c r="J122" s="6" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
       </c>
-      <c r="K122" s="7" t="inlineStr">
+      <c r="K122" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="7" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>FD-QB-002</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>Verify the QuickBooks line description equals the adjustment name and the item is the mapped Fee/Discount item</t>
         </is>
       </c>
-      <c r="E123" s="7" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F123" s="7" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G123" s="7" t="inlineStr">
+      <c r="G123" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H123" s="7" t="inlineStr">
+      <c r="H123" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I123" s="7" t="inlineStr">
+      <c r="I123" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J123" s="7" t="inlineStr">
+      <c r="J123" s="6" t="inlineStr">
         <is>
           <t>S6-R3, S6-R5</t>
         </is>
       </c>
-      <c r="K123" s="7" t="inlineStr">
+      <c r="K123" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="7" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>FD-QB-003</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>QuickBooks sync — edge</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D124" s="6" t="inlineStr">
         <is>
           <t>Verify a $0.00 resolved adjustment is skipped when sent to QuickBooks</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="E124" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G124" s="7" t="inlineStr">
+      <c r="G124" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H124" s="7" t="inlineStr">
+      <c r="H124" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I124" s="7" t="inlineStr">
+      <c r="I124" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J124" s="7" t="inlineStr">
+      <c r="J124" s="6" t="inlineStr">
         <is>
           <t>S6-R1, §5-R8</t>
         </is>
       </c>
-      <c r="K124" s="7" t="inlineStr">
+      <c r="K124" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="7" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>FD-QB-004</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>Verify adding a fee is blocked when the Fee item is unmapped (exact message)</t>
         </is>
       </c>
-      <c r="E125" s="7" t="inlineStr">
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G125" s="7" t="inlineStr">
+      <c r="G125" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H125" s="7" t="inlineStr">
+      <c r="H125" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I125" s="7" t="inlineStr">
+      <c r="I125" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J125" s="7" t="inlineStr">
+      <c r="J125" s="6" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6a, S6-R6d</t>
         </is>
       </c>
-      <c r="K125" s="7" t="inlineStr">
+      <c r="K125" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="7" t="inlineStr">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>FD-QB-005</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>Verify adding a discount is blocked when the Discount item is unmapped (exact message)</t>
         </is>
       </c>
-      <c r="E126" s="7" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F126" s="7" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G126" s="7" t="inlineStr">
+      <c r="G126" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H126" s="7" t="inlineStr">
+      <c r="H126" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I126" s="7" t="inlineStr">
+      <c r="I126" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J126" s="7" t="inlineStr">
+      <c r="J126" s="6" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6d</t>
         </is>
       </c>
-      <c r="K126" s="7" t="inlineStr">
+      <c r="K126" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>FD-QB-006</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>Verify the mapping guard blocks adds on every add surface (WO, labor line, part, part sale, template-apply)</t>
         </is>
       </c>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F127" s="7" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="G127" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H127" s="7" t="inlineStr">
+      <c r="H127" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I127" s="7" t="inlineStr">
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J127" s="7" t="inlineStr">
+      <c r="J127" s="6" t="inlineStr">
         <is>
           <t>S6-R6a</t>
         </is>
       </c>
-      <c r="K127" s="7" t="inlineStr">
+      <c r="K127" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="7" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>FD-QB-007</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>Verify an auto-apply default cannot be saved while the matching QuickBooks item is unmapped</t>
         </is>
       </c>
-      <c r="E128" s="7" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F128" s="7" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G128" s="7" t="inlineStr">
+      <c r="G128" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H128" s="7" t="inlineStr">
+      <c r="H128" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I128" s="7" t="inlineStr">
+      <c r="I128" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J128" s="7" t="inlineStr">
+      <c r="J128" s="6" t="inlineStr">
         <is>
           <t>S6-R6b</t>
         </is>
       </c>
-      <c r="K128" s="7" t="inlineStr">
+      <c r="K128" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>FD-QB-008</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>Verify creating/editing a non-auto-apply template is always allowed and no block exists when QuickBooks is not connected</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G129" s="7" t="inlineStr">
+      <c r="G129" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H129" s="7" t="inlineStr">
+      <c r="H129" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I129" s="7" t="inlineStr">
+      <c r="I129" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J129" s="7" t="inlineStr">
+      <c r="J129" s="6" t="inlineStr">
         <is>
           <t>S6-R6c</t>
         </is>
       </c>
-      <c r="K129" s="7" t="inlineStr">
+      <c r="K129" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>FD-QB-009</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr">
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>Verify unmapping an in-use item routes affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
-      <c r="E130" s="7" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F130" s="7" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G130" s="7" t="inlineStr">
+      <c r="G130" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H130" s="7" t="inlineStr">
+      <c r="H130" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I130" s="7" t="inlineStr">
+      <c r="I130" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J130" s="7" t="inlineStr">
+      <c r="J130" s="6" t="inlineStr">
         <is>
           <t>S6-R7, S6-R7a</t>
         </is>
       </c>
-      <c r="K130" s="7" t="inlineStr">
+      <c r="K130" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="7" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>FD-QB-010</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — Class</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>Verify a single QuickBooks Class applies to every synced line including fee/discount lines</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F131" s="7" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G131" s="7" t="inlineStr">
+      <c r="G131" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H131" s="7" t="inlineStr">
+      <c r="H131" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I131" s="7" t="inlineStr">
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J131" s="7" t="inlineStr">
+      <c r="J131" s="6" t="inlineStr">
         <is>
           <t>S6-R8</t>
         </is>
       </c>
-      <c r="K131" s="7" t="inlineStr">
+      <c r="K131" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>FD-QB-011</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — Class validation</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>Verify a deleted/deactivated Class aborts the entire invoice sync (no substitution)</t>
         </is>
       </c>
-      <c r="E132" s="7" t="inlineStr">
+      <c r="E132" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F132" s="7" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G132" s="7" t="inlineStr">
+      <c r="G132" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H132" s="7" t="inlineStr">
+      <c r="H132" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I132" s="7" t="inlineStr">
+      <c r="I132" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J132" s="7" t="inlineStr">
+      <c r="J132" s="6" t="inlineStr">
         <is>
           <t>S6-R9</t>
         </is>
       </c>
-      <c r="K132" s="7" t="inlineStr">
+      <c r="K132" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
@@ -8098,57 +8098,57 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="7" t="inlineStr">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>FD-QB-013</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
+      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>Verify discount lines to QuickBooks are capped with largest-remainder whole-cent penny allocation</t>
         </is>
       </c>
-      <c r="E134" s="7" t="inlineStr">
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F134" s="7" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G134" s="7" t="inlineStr">
+      <c r="G134" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H134" s="7" t="inlineStr">
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I134" s="7" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J134" s="7" t="inlineStr">
+      <c r="J134" s="6" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="K134" s="7" t="inlineStr">
+      <c r="K134" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
@@ -8269,57 +8269,57 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="7" t="inlineStr">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>FD-QB-016</t>
         </is>
       </c>
-      <c r="B137" s="7" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C137" s="7" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>QuickBooks sync — tax</t>
         </is>
       </c>
-      <c r="D137" s="7" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>Verify a synced line's tax follows the adjustment's taxable setting</t>
         </is>
       </c>
-      <c r="E137" s="7" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F137" s="7" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G137" s="7" t="inlineStr">
+      <c r="G137" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H137" s="7" t="inlineStr">
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I137" s="7" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J137" s="7" t="inlineStr">
+      <c r="J137" s="6" t="inlineStr">
         <is>
           <t>S6-R2, §5-R11</t>
         </is>
       </c>
-      <c r="K137" s="7" t="inlineStr">
+      <c r="K137" s="6" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
@@ -8497,57 +8497,57 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="7" t="inlineStr">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>FD-HIST-004</t>
         </is>
       </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
         <is>
           <t>History log — visibility</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr">
+      <c r="D141" s="6" t="inlineStr">
         <is>
           <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the feature flag</t>
         </is>
       </c>
-      <c r="E141" s="7" t="inlineStr">
+      <c r="E141" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F141" s="7" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G141" s="7" t="inlineStr">
+      <c r="G141" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H141" s="7" t="inlineStr">
+      <c r="H141" s="6" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I141" s="7" t="inlineStr">
+      <c r="I141" s="6" t="inlineStr">
         <is>
           <t>Environment window — flag-off history visibility (org flag toggle skipped on shared env).</t>
         </is>
       </c>
-      <c r="J141" s="7" t="inlineStr">
+      <c r="J141" s="6" t="inlineStr">
         <is>
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="K141" s="7" t="inlineStr">
+      <c r="K141" s="6" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
@@ -9295,59 +9295,59 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>FD-CALC-010</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Verify a negative base is treated as $0 (resolved amount = $0.00, base never goes below zero)</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
         <is>
           <t>§5-R3, §5-R4</t>
         </is>
       </c>
-      <c r="K155" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -9922,59 +9922,59 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>FD-PERM-004</t>
         </is>
       </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="B166" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C166" s="5" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>Verify Part-Sale part adjustment add/edit/remove requires Part Sales: Create and Edit</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F166" s="6" t="inlineStr">
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-NotBuilt</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G166" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED — NEEDS-ACCOUNT</t>
-        </is>
-      </c>
-      <c r="H166" s="6" t="inlineStr">
-        <is>
-          <t>QA (restricted-role session)</t>
-        </is>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>Restricted-role login (tech quick-login flaky on qb) or a self-service staff role-switch: Story 13 — Part-Sale adjustment permission (needs a non-Tech role login).</t>
-        </is>
-      </c>
-      <c r="J166" s="6" t="inlineStr">
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEV NOT BUILT</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>Dev team</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
         <is>
           <t>S13-R5</t>
         </is>
       </c>
-      <c r="K166" s="6" t="inlineStr">
-        <is>
-          <t>needs-account</t>
+      <c r="K166" s="5" t="inlineStr">
+        <is>
+          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
         </is>
       </c>
     </row>
@@ -10150,59 +10150,59 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="6" t="inlineStr">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>FD-PERM-008</t>
         </is>
       </c>
-      <c r="B170" s="6" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C170" s="6" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G170" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED — NEEDS-ACCOUNT</t>
-        </is>
-      </c>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>QA (restricted-role session)</t>
-        </is>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>Restricted-role login (tech quick-login flaky on qb) or a self-service staff role-switch: Story 13 — customer-default view/change gate (Manage AP/AR + Cust Mgmt); needs the specific role.</t>
-        </is>
-      </c>
-      <c r="J170" s="6" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="K170" s="6" t="inlineStr">
-        <is>
-          <t>needs-account</t>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -10264,59 +10264,59 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="6" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>FD-PERM-010</t>
         </is>
       </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C172" s="6" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F172" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED — NEEDS-ACCOUNT</t>
-        </is>
-      </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t>QA (restricted-role session)</t>
-        </is>
-      </c>
-      <c r="I172" s="6" t="inlineStr">
-        <is>
-          <t>Restricted-role login (tech quick-login flaky on qb) or a self-service staff role-switch: Story 13 — BOTH gates required (flag + permission) proven per-role; needs a restricted account.</t>
-        </is>
-      </c>
-      <c r="J172" s="6" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
         <is>
           <t>S13-R1, feature flag + permission (both gates)</t>
         </is>
       </c>
-      <c r="K172" s="6" t="inlineStr">
-        <is>
-          <t>needs-account</t>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -10378,171 +10378,171 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="7" t="inlineStr">
+      <c r="A174" s="6" t="inlineStr">
         <is>
           <t>FD-FLAG-001</t>
         </is>
       </c>
-      <c r="B174" s="7" t="inlineStr">
+      <c r="B174" s="6" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C174" s="7" t="inlineStr">
+      <c r="C174" s="6" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D174" s="7" t="inlineStr">
+      <c r="D174" s="6" t="inlineStr">
         <is>
           <t>Verify with the FeesAndDiscounts flag OFF, all F&amp;D UI and behavior are hidden everywhere</t>
         </is>
       </c>
-      <c r="E174" s="7" t="inlineStr">
+      <c r="E174" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F174" s="7" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G174" s="7" t="inlineStr">
+      <c r="G174" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H174" s="7" t="inlineStr">
+      <c r="H174" s="6" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I174" s="7" t="inlineStr">
+      <c r="I174" s="6" t="inlineStr">
         <is>
           <t>Environment window — flag-off window (org-level FeesAndDiscounts toggle skipped on shared env).</t>
         </is>
       </c>
-      <c r="J174" s="7" t="inlineStr">
+      <c r="J174" s="6" t="inlineStr">
         <is>
           <t>§1 feature flag, S13-R1</t>
         </is>
       </c>
-      <c r="K174" s="7" t="inlineStr">
+      <c r="K174" s="6" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="7" t="inlineStr">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>FD-FLAG-002</t>
         </is>
       </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C175" s="7" t="inlineStr">
+      <c r="C175" s="6" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D175" s="7" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t>Verify the WO history log STILL shows fee/discount entries even when the feature flag is OFF</t>
         </is>
       </c>
-      <c r="E175" s="7" t="inlineStr">
+      <c r="E175" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G175" s="7" t="inlineStr">
+      <c r="G175" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H175" s="7" t="inlineStr">
+      <c r="H175" s="6" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I175" s="7" t="inlineStr">
+      <c r="I175" s="6" t="inlineStr">
         <is>
           <t>Environment window — flag-off exception (history log visible with flag off).</t>
         </is>
       </c>
-      <c r="J175" s="7" t="inlineStr">
+      <c r="J175" s="6" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="K175" s="7" t="inlineStr">
+      <c r="K175" s="6" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="7" t="inlineStr">
+      <c r="A176" s="6" t="inlineStr">
         <is>
           <t>FD-FLAG-003</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr">
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr">
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D176" s="7" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
         <is>
           <t>Verify with the flag ON, the matching permission is still required to use F&amp;D</t>
         </is>
       </c>
-      <c r="E176" s="7" t="inlineStr">
+      <c r="E176" s="6" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F176" s="7" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G176" s="7" t="inlineStr">
+      <c r="G176" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H176" s="7" t="inlineStr">
+      <c r="H176" s="6" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I176" s="7" t="inlineStr">
+      <c r="I176" s="6" t="inlineStr">
         <is>
           <t>Environment window — flag ON + permission-required interaction (flag-side complement).</t>
         </is>
       </c>
-      <c r="J176" s="7" t="inlineStr">
+      <c r="J176" s="6" t="inlineStr">
         <is>
           <t>§1 feature flag + S13-R1</t>
         </is>
       </c>
-      <c r="K176" s="7" t="inlineStr">
+      <c r="K176" s="6" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
@@ -10967,47 +10967,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Fees &amp; Discounts V1 — Blockers Tracker · Summary</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Total authored cases</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="8" t="n">
         <v>182</v>
       </c>
-      <c r="C3" s="9" t="n"/>
+      <c r="C3" s="8" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -11059,30 +11059,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Dev / QA env (QuickBooks, flag-off)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>BLOCKED — NEEDS-ACCOUNT</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>QA (restricted-role session)</t>
         </is>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -11112,12 +11112,12 @@
       <c r="B12" s="11" t="n">
         <v>182</v>
       </c>
-      <c r="C12" s="9" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -11130,45 +11130,45 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -11181,45 +11181,45 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>code-bug</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>PO-question</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -11232,34 +11232,34 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="B25" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Story 8 — Processing-Fee builder UI (SV-73xx)</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="9" t="n"/>
+      <c r="C26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -11272,34 +11272,34 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n"/>
+      <c r="C28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C29" s="9" t="n"/>
+      <c r="C29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="9" t="n"/>
+      <c r="C30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -11307,8 +11307,8 @@
           <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -11316,12 +11316,12 @@
           <t>• Fresh qb QA cookies (admin; tech quick-login is FLAKY — retest each run)</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>unblocks the 34 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 4 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>unblocks the 24 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -11329,12 +11329,12 @@
           <t>• Dev deploys Story 8 (Processing-Fee builder UI) + Story 11 (Part Sales fees/discounts)</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>unblocks the 11 DEV-NOT-BUILT cases (Story 8 = 4, Story 11 = 7); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>unblocks the 12 DEV-NOT-BUILT cases (Story 8 = 4, Story 11 = 8); then QA re-runs VIU.</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -11342,12 +11342,12 @@
           <t>• A QuickBooks-connected env (or dev/QB-side inspection) for Story 6</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>unblocks the 13 QuickBooks ENV cases (mapping guard, sync, negative-total credit memo).</t>
         </is>
       </c>
-      <c r="C35" s="9" t="n"/>
+      <c r="C35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -11355,12 +11355,12 @@
           <t>• A flag-off maintenance window on a non-shared env</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>unblocks the 5 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n"/>
+      <c r="C36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -11368,12 +11368,12 @@
           <t>• PO/dev rulings on the deviations + double-add + NOTE-FD-4</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 17 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n"/>
+      <c r="C37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -11381,12 +11381,12 @@
           <t>• Restricted-role accounts (or confirmation the self-service staff role-switch is usable on qb)</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>unblocks the 4 NEEDS-ACCOUNT Story-13 per-role negatives (restore Tech afterward).</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="n"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>unblocks the 0 NEEDS-ACCOUNT Story-13 per-role negatives (restore Tech afterward).</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -1828,59 +1828,59 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>FD-PART-001</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>S1-R4 / S1-R5 / S2-R11</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -1942,59 +1942,59 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>FD-PART-003</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>S1-R4 / §5-R13</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -2113,116 +2113,116 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>FD-PART-006</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>§5-R12</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>FD-PART-007</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Verify deleting a part removes any adjustment pointing to it</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>S3-R2</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -6787,59 +6787,59 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>FD-DOC-001</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>S5-R1</t>
         </is>
       </c>
-      <c r="K111" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -6901,59 +6901,59 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>FD-DOC-003</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>Customer document — per-line adjustments</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
         <is>
           <t>S5-R2, S5-R3</t>
         </is>
       </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -7072,59 +7072,59 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>FD-DOC-006</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>S5-R7, S5-R8</t>
         </is>
       </c>
-      <c r="K116" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -7300,59 +7300,59 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>FD-DOC-010</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>Customer document — line-level $0 target</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I120" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
         <is>
           <t>§5-R12</t>
         </is>
       </c>
-      <c r="K120" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="8" t="n"/>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 24 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 16 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 17 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 18 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -802,59 +802,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FD-WO-005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Verify the Add button is disabled until Name, Type, Calculation type and Amount&gt;0 are all set</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>QA + PO ruling</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Batch-2 flagged as a deviation for PO confirmation, not rewritten — BUG-FD-4 — Add-dialog 'Add' button not disabled on an empty form (inline-error vs disabled-button).</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Design §6 validateForm() / S2-N1 / S2-N2</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>pending (PO-flagged deviation)</t>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -2398,59 +2398,59 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>FD-INLINE-003</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Verify a line/part with 2+ adjustments shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>QA + PO ruling</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Batch-2 flagged as a deviation for PO confirmation, not rewritten — BUG-FD-5 — no 'Show N more' collapse when a line has ≥2 adjustments.</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>S3-R15 / S3-R16 / S12-R6</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>pending (PO-flagged deviation)</t>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -2626,59 +2626,59 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FD-STATS-002</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Verify each Stats F&amp;D row shows a scope hyperlink naming its target</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>QA + PO ruling</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Batch-2 flagged as a deviation for PO confirmation, not rewritten — BUG-FD-2 — Stats aggregate layout blocks per-adjustment row verification.</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>S4-R3 / design §3</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>pending (PO-flagged deviation)</t>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -2740,59 +2740,59 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>FD-STATS-004</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Verify the Stats F&amp;D rows are listed in creation order (oldest first)</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>QA + PO ruling</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Batch-2 flagged as a deviation for PO confirmation, not rewritten — BUG-FD-2 — Stats aggregate blocks creation-order row verification.</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>§5-R9</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>pending (PO-flagged deviation)</t>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -4279,59 +4279,59 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>FD-CUST-005</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Verify the picker lists only unlinked templates and shows Processing Fee templates as type "Fee"</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>QA + PO ruling</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>Batch-2 flagged as a deviation for PO confirmation, not rewritten — NOTE-FD-5 — customer-default picker is a single-select dropdown, not a multi-select checkbox list.</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>pending (PO-flagged deviation)</t>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -10549,59 +10549,59 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>FD-VAL-001</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Verify the Add button stays DISABLED until Name AND Type AND Calculation type AND Amount &gt; 0 are all set</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>QA + PO ruling</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>Batch-2 flagged as a deviation for PO confirmation, not rewritten — BUG-FD-4 — Add button enabled on empty form; build validates on submit.</t>
-        </is>
-      </c>
-      <c r="J177" s="4" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
         </is>
       </c>
-      <c r="K177" s="4" t="inlineStr">
-        <is>
-          <t>pending (PO-flagged deviation)</t>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C22" s="8" t="n"/>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 16 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 10 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 18 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 24 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Verify multi-select adding of several templates at once shows the plural toast</t>
+          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>S9-R20, S9-R21, S9-R23b</t>
+          <t>S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default via the row menu needs no confirm and toasts</t>
+          <t>Verify removing a customer default via the row's remove action needs no confirm and toasts</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -6673,116 +6673,116 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>FD-PROC-013</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>Processing Fee — calculation edge</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
         <is>
           <t>§5-R4 (multiple Processing Fees)</t>
         </is>
       </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>FD-PROC-014</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>Processing Fee — negative</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>S8-N6</t>
         </is>
       </c>
-      <c r="K110" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -8041,59 +8041,59 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>FD-QB-012</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G133" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
         <is>
           <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
         </is>
       </c>
-      <c r="K133" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -8155,59 +8155,59 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>FD-QB-014</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="K135" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -8668,59 +8668,59 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>FD-HIST-007</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>History log — Processing Fee</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee is logged as a fee with "Full invoice" applied-to and no "updated" entry</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
         </is>
       </c>
-      <c r="K144" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>case-update</t>
         </is>
       </c>
     </row>
@@ -9580,173 +9580,173 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>FD-CALC-015</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Verify negative-total floor at $0.00 — non-taxable $150 discount on $100 parts + $10 tax: subtotal floors, customer pays $10, $50 excess → tax-exempt goodwill credit</t>
         </is>
       </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>FD-CALC-016</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Verify a TAXABLE $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>S6-R10c</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>FD-CALC-017</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>Verify multiple discount lines are penny-capped via largest-remainder so capped discounts sum exactly to the floored net subtotal (no negative, whole-cent)</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
-        </is>
-      </c>
-      <c r="K160" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-016</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>Verify a TAXABLE $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>S6-R10c</t>
-        </is>
-      </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-017</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>Verify multiple discount lines are penny-capped via largest-remainder so capped discounts sum exactly to the floored net subtotal (no negative, whole-cent)</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>Environment window — environment limitation on the shared qb env.</t>
+        </is>
+      </c>
+      <c r="J162" s="6" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="K162" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO (known double-add bug)</t>
+          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" s="8" t="n"/>
     </row>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="8" t="n"/>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 10 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 2 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 5 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
+          <t>unblocks the 6 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 24 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 26 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -7357,59 +7357,59 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>FD-DOC-011</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>Customer document — layout</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-1 (MAJOR) — WO/estimate Subtotal/Total exclude adjustments while GST taxes them.</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
         <is>
           <t>S5-R5</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>code-bug</t>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
         </is>
       </c>
     </row>
@@ -8212,59 +8212,59 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>FD-QB-015</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit memo</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Dev / QA env</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
         <is>
           <t>S6-R11, S6-R13</t>
         </is>
       </c>
-      <c r="K136" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>quickbooks</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="8" t="n"/>
     </row>
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C29" s="8" t="n"/>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 2 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 13 QuickBooks ENV cases (mapping guard, sync, negative-total credit memo).</t>
+          <t>unblocks the 14 QuickBooks ENV cases (mapping guard, sync, negative-total credit memo).</t>
         </is>
       </c>
       <c r="C35" s="8" t="n"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 7 code-bug deviations; QA updates the 26 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 6 code-bug deviations; QA updates the 26 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -1648,10 +1648,14 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>pending-create</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr"/>
+          <t>29441</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -1658,67 +1658,67 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>FD-LABOR-001</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Verify a labor line's 3-dot menu opens the Add dialog locked to that Labor Line scope</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Verify a labor line's ⋮ menu opens the Add Fee/Discount dialog locked to that labor line</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>S1-R3 / S2-R10</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>28439</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line % of Labor Total fee resolves against the line's gross labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row exposes its own 3-dot menu on hover</t>
+          <t>Verify each labor line row shows its own ⋮ menu on hover</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line Flat Amount resolves to the exact amount with no quantity multiplier</t>
+          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment resolves to $0.00 when its line is not billable (declined)</t>
+          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any adjustment pointing to it</t>
+          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line 'Add fee / discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify the labor-line 'Add Fee/Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2127,67 +2127,67 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>FD-PART-001</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Verify a part's ⋮ menu opens the Add Fee/Discount dialog locked to that part</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>S1-R4 / S1-R5 / S2-R11</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>28446</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line Flat Amount is charged PER ITEM (amount × quantity): $5.00 × qty 3 → −$15.00</t>
+          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line % of Parts Total resolves against quantity × sell price (gross)</t>
+          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment stays attached when the part changes from requested to received</t>
+          <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any adjustment pointing to it</t>
+          <t>Verify deleting a part removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Verify per-item Flat Amount edge: quantity 1 resolves to the base amount (−$5.00)</t>
+          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single adjustment's name and rate</t>
+          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has multiple adjustments</t>
+          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has several fees/discounts</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no adjustments</t>
+          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no fees/discounts</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Verify clicking a populated 'Fees &amp; Discounts' cell opens the per-part breakdown modal with the correct columns</t>
+          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Verify the breakdown modal 'Net adjustment' row equals the signed sum of the part's adjustments</t>
+          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Verify a per-row Remove (trash) on the breakdown modal removes the adjustment and closes the modal when the last is removed</t>
+          <t>Verify a per-row Remove on the breakdown removes the fee/discount and closes when the last one is removed</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Verify the '+ Add' button is disabled on a part when the sale/WO cannot be edited</t>
+          <t>Verify the '+ Add' button is disabled when the sale/work order cannot be edited</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple adjustments on one part each resolve on the part's own base (do not compound) and net correctly</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-WO percentage adjustments resolve against the same net totals and do not change each other's base</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer "Fees &amp; Discounts (N)" tab shows the correct default count</t>
+          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Verify the "Default Fees &amp; Discounts" card header, caption, and table columns</t>
+          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4874,134 +4874,134 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>FD-CUST-003</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>S9-R18, S9-R19, S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>28487</t>
         </is>
       </c>
-      <c r="M66" s="3" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>FD-CUST-004</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>28488</t>
         </is>
       </c>
-      <c r="M67" s="3" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
         </is>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Verify the picker lists only unlinked templates and shows Processing Fee templates as type "Fee"</t>
+          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Verify the empty picker message when there are no templates left to add</t>
+          <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5142,67 +5142,67 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>FD-CUST-007</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Verify removing a customer default via the row's remove action needs no confirm and toasts</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Verify removing a customer default from the row needs no confirmation</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>S9-R16, S9-R24</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>28491</t>
         </is>
       </c>
-      <c r="M70" s="3" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
         </is>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Verify a customer default is added as an independent adjustment on every NEW work order</t>
+          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage customer default re-resolves per work order (keeps percent, not a fixed dollar)</t>
+          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default does NOT change adjustments already on existing work orders</t>
+          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template that is a customer default drops the default link but keeps existing WO adjustments</t>
+          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Verify a newly created customer inherits every auto-apply location template as a default</t>
+          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer Fees &amp; Discounts tab and controls are hidden without the required permissions</t>
+          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only ONCE to a new WO</t>
+          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Verify add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5879,67 +5879,67 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-001</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Template admin — location</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>S7-R7a, S7-R7c</t>
         </is>
       </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>28502</t>
         </is>
       </c>
-      <c r="M81" s="3" t="inlineStr">
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the delete action</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -6013,134 +6013,134 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-003</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
         </is>
       </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>28504</t>
         </is>
       </c>
-      <c r="M83" s="3" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-004</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Verify creating a Discount template shows the "Discount added" toast</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Verify creating a Discount template</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>S7-R12a, S7-R18a</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>28505</t>
         </is>
       </c>
-      <c r="M84" s="3" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
+          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -6214,67 +6214,67 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-006</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Template admin — edit</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
         </is>
       </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>28507</t>
         </is>
       </c>
-      <c r="M86" s="3" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog copy and buttons</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -6348,67 +6348,67 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-008</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>S7-R21</t>
         </is>
       </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>28509</t>
         </is>
       </c>
-      <c r="M88" s="3" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure toast</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Verify template Name enforces the 100-character limit</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Verify "Processing Fee" is a third type in the template builder (template-only)</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount (default) and % of Grand Total, with a tax-inclusive base</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for every Processing Fee (both methods)</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable control defaults Yes and shows the §5-R15 jurisdiction note</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a WO can be removed but not edited</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee +, discount −)</t>
+          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Verify the QuickBooks line description equals the adjustment name and the item is the mapped Fee/Discount item</t>
+          <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Verify a $0.00 resolved adjustment is skipped when sent to QuickBooks</t>
+          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Verify adding a fee is blocked when the Fee item is unmapped (exact message)</t>
+          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Verify adding a discount is blocked when the Discount item is unmapped (exact message)</t>
+          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Verify the mapping guard blocks adds on every add surface (WO, labor line, part, part sale, template-apply)</t>
+          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Verify an auto-apply default cannot be saved while the matching QuickBooks item is unmapped</t>
+          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Verify creating/editing a non-auto-apply template is always allowed and no block exists when QuickBooks is not connected</t>
+          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Verify unmapping an in-use item routes affected invoices to Unexported Items (recoverable, no data lost)</t>
+          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Verify a single QuickBooks Class applies to every synced line including fee/discount lines</t>
+          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Verify a deleted/deactivated Class aborts the entire invoice sync (no substitution)</t>
+          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Verify discount lines to QuickBooks are capped with largest-remainder whole-cent penny allocation</t>
+          <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit memo</t>
+          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Verify a synced line's tax follows the adjustment's taxable setting</t>
+          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -9765,536 +9765,536 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>FD-HIST-001</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>History log</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>28560</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-002</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>History log</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>28561</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-003</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>History log</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>S10-R3, S10-R5</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>28562</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>FD-HIST-004</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>History log — visibility</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Verify fee/discount history stays visible when the fee/discount screens are hidden by the feature being off</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
-        </is>
-      </c>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>28560</t>
-        </is>
-      </c>
-      <c r="M139" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>FD-HIST-002</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>Environment window — flag-off history visibility (org flag toggle skipped on shared env).</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>S10-R1</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L142" s="6" t="inlineStr">
+        <is>
+          <t>28563</t>
+        </is>
+      </c>
+      <c r="M142" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-005</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>History log</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>Verify the history detail block shows Name, Type, Amount (set rate), and Applied-to label</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I140" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
-        </is>
-      </c>
-      <c r="K140" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>28561</t>
-        </is>
-      </c>
-      <c r="M140" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>FD-HIST-003</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>History log — visibility</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>S10-R1, S10-R6c, S13-R10</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>28564</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-006</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>History log</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>Verify an adjustment entry leaves the saved-state icon empty and the Line column shows "−"</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>S10-R3, S10-R5</t>
-        </is>
-      </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>28562</t>
-        </is>
-      </c>
-      <c r="M141" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>FD-HIST-004</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>History log — permission</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>S13-R10</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>28565</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-007</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>History log — visibility</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the feature flag</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>S10-R1</t>
-        </is>
-      </c>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>28563</t>
-        </is>
-      </c>
-      <c r="M142" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>FD-HIST-005</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>History log — Processing Fee</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>28566</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-008</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>History log — visibility</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>Verify F&amp;D history stays visible when the F&amp;D UI is hidden by See Financial Data being off</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>S10-R1, S10-R6c, S13-R10</t>
-        </is>
-      </c>
-      <c r="K143" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>28564</t>
-        </is>
-      </c>
-      <c r="M143" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>FD-HIST-006</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>History log — permission</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>S13-R10</t>
-        </is>
-      </c>
-      <c r="K144" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>28565</t>
-        </is>
-      </c>
-      <c r="M144" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>FD-HIST-007</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>History log — Processing Fee</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee is logged as a fee with "Full invoice" applied-to and no "updated" entry</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I145" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
-        </is>
-      </c>
-      <c r="K145" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>28566</t>
-        </is>
-      </c>
-      <c r="M145" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>FD-HIST-008</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>History log — edit entry</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G146" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>S10-R6c, S2-R6</t>
         </is>
       </c>
-      <c r="K146" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
         <is>
           <t>28567</t>
         </is>
       </c>
-      <c r="M146" s="4" t="inlineStr">
+      <c r="M146" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage adjustment resolves as base × percent (10% fee on $150.00 → +$15.00)</t>
+          <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Verify percentage rounding — half a cent or more rounds UP (5% discount on $33.33 → $1.6665 → −$1.67)</t>
+          <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Verify a Flat Amount on Whole-WO or Labor Line resolves to the set amount exactly (no quantity multiplier)</t>
+          <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Verify a Flat Amount on a Part Line is PER ITEM (amount × quantity: $5.00 × qty 3 → −$15.00; qty 1 → −$5.00)</t>
+          <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount cannot exceed 100% (fee percentages have no upper limit)</t>
+          <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Verify minimum values — Flat Amount smallest is $0.01, Percentage smallest is 0.01%</t>
+          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount clamps a percentage result (20% fee on $100 → $20 → Max $15 → +$15.00)</t>
+          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Verify Max Amount = $0 forces resolve to $0.00, while blank/empty Max Amount means no cap</t>
+          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 base resolves to $0.00 and the $0.00 line is skipped in QuickBooks (still shown on screens)</t>
+          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Verify a negative base is treated as $0 (resolved amount = $0.00, base never goes below zero)</t>
+          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable adjustment does not change tax</t>
+          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Verify the 3-step resolution ORDER — line-level on gross first, whole-WO on net second, no stacking within a step</t>
+          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee resolves LAST on the tax-inclusive Grand Total (3% of $324 → +$9.72)</t>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Verify negative-total floor at $0.00 — non-taxable $150 discount on $100 parts + $10 tax: subtotal floors, customer pays $10, $50 excess → tax-exempt goodwill credit</t>
+          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Verify a TAXABLE $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>Verify multiple discount lines are penny-capped via largest-remainder so capped discounts sum exactly to the floored net subtotal (no negative, whole-cent)</t>
+          <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Verify Part-Sale adjustment add/edit/remove (whole sale or part line) requires Part Sales: Create and Edit + See Financial Data</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -11976,67 +11976,67 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>FD-PERM-009</t>
         </is>
       </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>Verify seeing fee/discount entries in the WO history log requires Work Orders: Create and Edit (line history requires Work Order Lines: Create and Edit)</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I172" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
         <is>
           <t>28593</t>
         </is>
       </c>
-      <c r="M172" s="4" t="inlineStr">
+      <c r="M172" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>Verify with the FeesAndDiscounts flag OFF, all F&amp;D UI and behavior are hidden everywhere</t>
+          <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -12244,67 +12244,67 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="A176" s="6" t="inlineStr">
         <is>
           <t>FD-FLAG-002</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
-        <is>
-          <t>Verify the WO history log STILL shows fee/discount entries even when the feature flag is OFF</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>Verify the work-order history still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>QA (V1_2 re-VIU)</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr">
-        <is>
-          <t>V1_2 spec change — EXPECTED updated (S13-R10 history gating / §5-R15 note); needs a live re-VIU (re-derive the qb roles matrix first; tech quick-login flaky).</t>
-        </is>
-      </c>
-      <c r="J176" s="4" t="inlineStr">
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>Environment window — flag-off exception (history log visible with flag off).</t>
+        </is>
+      </c>
+      <c r="J176" s="6" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="K176" s="4" t="inlineStr">
-        <is>
-          <t>v1_2-retest</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
+      <c r="K176" s="6" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L176" s="6" t="inlineStr">
         <is>
           <t>28597</t>
         </is>
       </c>
-      <c r="M176" s="4" t="inlineStr">
+      <c r="M176" s="6" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
         </is>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>Verify with the flag ON, the matching permission is still required to use F&amp;D</t>
+          <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -12919,7 +12919,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C22" s="8" t="n"/>
     </row>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" s="8" t="n"/>
     </row>
@@ -13217,7 +13217,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 11 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 4 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
+          <t>unblocks the 6 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 5 code-bug deviations; QA updates the 22 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 5 code-bug deviations; QA updates the 12 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -6549,67 +6549,67 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-011</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>S7-R12e, S7-R14, §5-R6</t>
         </is>
       </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>28512</t>
         </is>
       </c>
-      <c r="M91" s="3" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
@@ -9564,67 +9564,67 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>FD-QB-014</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>reachable/needs-data</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
         <is>
           <t>28557</t>
         </is>
       </c>
-      <c r="M136" s="3" t="inlineStr">
+      <c r="M136" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
@@ -10636,67 +10636,67 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>FD-CALC-006</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-10 — percent below minimum silently coerced up instead of rejected.</t>
-        </is>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>§5-R1</t>
         </is>
       </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="L152" s="3" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
         <is>
           <t>28573</t>
         </is>
       </c>
-      <c r="M152" s="3" t="inlineStr">
+      <c r="M152" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28573</t>
         </is>
@@ -10770,67 +10770,67 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>FD-CALC-008</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-9 — maxCap 0 accepted and treated as NO cap (should force $0.00).</t>
-        </is>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>§5-R6</t>
         </is>
       </c>
-      <c r="K154" s="3" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
         <is>
           <t>28575</t>
         </is>
       </c>
-      <c r="M154" s="3" t="inlineStr">
+      <c r="M154" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28575</t>
         </is>
@@ -12713,67 +12713,67 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>FD-VAL-006</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I183" s="3" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-9 — maxCap 0 not treated as empty/never-sent.</t>
-        </is>
-      </c>
-      <c r="J183" s="3" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>§5-R6, S2-R24, S2-R25</t>
         </is>
       </c>
-      <c r="K183" s="3" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
         <is>
           <t>28604</t>
         </is>
       </c>
-      <c r="M183" s="3" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
@@ -12919,7 +12919,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C20" s="8" t="n"/>
     </row>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C22" s="8" t="n"/>
     </row>
@@ -13217,7 +13217,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 2 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 5 code-bug deviations; QA updates the 12 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 10 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -9564,67 +9564,67 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>FD-QB-014</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="K136" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
         <is>
           <t>28557</t>
         </is>
       </c>
-      <c r="M136" s="4" t="inlineStr">
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
@@ -12919,7 +12919,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>unblocks the 2 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when the fee/discount screens are hidden by the feature being off</t>
+          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Verify the work-order history still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
+          <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -9777,7 +9777,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>History log — permission</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>History log — Processing Fee</t>
+          <t>Audit log — Processing Fee</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>History log — edit entry</t>
+          <t>Audit log — edit entry</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -71,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,9 +114,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -124,6 +121,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M184"/>
+  <dimension ref="A1:M186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -854,67 +854,67 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FD-WO-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Design §6 validateForm() / S2-N1 / S2-N2</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>28428</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
         </is>
@@ -1591,67 +1591,67 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>FD-WO-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>S2-R26, S2-R26a, §5-R15</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>29441</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
         </is>
@@ -3668,469 +3668,469 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>FD-PCOL-001</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>S11-R10a / design §5</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>28469</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28469</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>FD-PCOL-002</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has several fees/discounts</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>S11-R10b / design §5</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>28470</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28470</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>FD-PCOL-003</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no fees/discounts</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>S11-R9 / design §5</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>28471</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28471</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>FD-PCOL-004</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Parts page — breakdown modal</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>S11-R11 / S11-R12 / S11-R13 / S11-R16</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>28472</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28472</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>FD-PCOL-005</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Parts page — breakdown modal</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>S11-R15</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>28473</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28473</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>FD-PCOL-006</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Parts page — breakdown modal</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Verify a per-row Remove on the breakdown removes the fee/discount and closes when the last one is removed</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>S11-R14 / S11-R17</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>28474</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28474</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>FD-PCOL-007</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Verify the '+ Add' button is disabled when the sale/work order cannot be edited</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>S11-R9 / S3-R1b</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>28475</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28475</t>
         </is>
@@ -4742,22 +4742,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-001</t>
+          <t>FD-PSALE-001</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>B (Customer/Admin/Finance)</t>
+          <t>A (WO/Parts)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>S9-R11</t>
+          <t>S11-R3 / S11-R4a / S11-R4b / §5-R15</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4797,19 +4797,19 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-002</t>
+          <t>FD-CUST-001</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
+          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>S9-R12, S9-R13, S9-R14, S9-R15, S12-R8</t>
+          <t>S9-R11</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4864,19 +4864,19 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-003</t>
+          <t>FD-CUST-002</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a single template as a customer default via the picker</t>
+          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>S9-R18, S9-R19, S9-R20, S9-R21, S9-R23a</t>
+          <t>S9-R12, S9-R13, S9-R14, S9-R15, S12-R8</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4931,287 +4931,287 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>28486</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>FD-CUST-003</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Customer Fees &amp; Discounts tab</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding a single template as a customer default via the picker</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>S9-R18, S9-R19, S9-R20, S9-R21, S9-R23a</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>28487</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>FD-CUST-004</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>28488</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>FD-CUST-005</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>28489</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>FD-CUST-005</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Customer Fees &amp; Discounts tab</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>case-update</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>28489</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
           <t>FD-CUST-006</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>S9-R22</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>28490</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>FD-CUST-007</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Verify removing a customer default from the row needs no confirmation</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>S9-R16, S9-R24</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>28491</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-008</t>
+          <t>FD-CUST-007</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
+          <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>S9-R17</t>
+          <t>S9-R16, S9-R24</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>28491</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-009</t>
+          <t>FD-CUST-008</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
+          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>S9-R2, S9-R3, S9-R4</t>
+          <t>S9-R17</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5333,19 +5333,19 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>28492</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-010</t>
+          <t>FD-CUST-009</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
+          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>S9-R6, S9-R7</t>
+          <t>S9-R2, S9-R3, S9-R4</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5400,19 +5400,19 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>28494</t>
+          <t>28493</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-011</t>
+          <t>FD-CUST-010</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
+          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>S9-R8</t>
+          <t>S9-R6, S9-R7</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5467,19 +5467,19 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-012</t>
+          <t>FD-CUST-011</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
+          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>S9-R9, S7-R4, S7-N1</t>
+          <t>S9-R8</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5534,19 +5534,19 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-013</t>
+          <t>FD-CUST-012</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a customer removes that customer's default links</t>
+          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>S9-R10</t>
+          <t>S9-R9, S7-R4, S7-N1</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -5601,19 +5601,19 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>28497</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-014</t>
+          <t>FD-CUST-013</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults seeding</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
+          <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>S9-R1</t>
+          <t>S9-R10</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5668,19 +5668,19 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-015</t>
+          <t>FD-CUST-014</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — permissions</t>
+          <t>Customer defaults seeding</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
+          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>S13-R9, S13-N3</t>
+          <t>S9-R1</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-016</t>
+          <t>FD-CUST-015</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults — known bug</t>
+          <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
+          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -5787,34 +5787,34 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Verified, but Double-add (BUG-FD-1) did NOT reproduce on batch-2 (backend dedupes) — PO to confirm the S9 fix shipped; re-scope to single adjustment.</t>
+          <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>S9 known gap (§14 item 4)</t>
+          <t>S13-R9, S13-N3</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>verified (PO-confirm)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-017</t>
+          <t>FD-CUST-016</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>API — Customer Fees &amp; Discounts tab — negative</t>
+          <t>Customer defaults — known bug</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5854,34 +5854,34 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>None — VIU-verified; uploadable now.</t>
+          <t>Verified, but Double-add (BUG-FD-1) did NOT reproduce on batch-2 (backend dedupes) — PO to confirm the S9 fix shipped; re-scope to single adjustment.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>S9-N1</t>
+          <t>S9 known gap (§14 item 4)</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>verified (PO-confirm)</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>28501</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-CUST-017</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>S7-R7a, S7-R7c</t>
+          <t>S9-N1</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5936,19 +5936,19 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>S7-R8, S12-R8</t>
+          <t>S7-R7a, S7-R7c</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6003,19 +6003,19 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>28502</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
+          <t>S7-R8, S12-R8</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6070,19 +6070,19 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>28504</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>S7-R12a, S7-R18a</t>
+          <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6137,19 +6137,19 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28504</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
+          <t>S7-R12a, S7-R18a</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6204,19 +6204,19 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
+          <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6271,19 +6271,19 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>28506</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>S7-R20</t>
+          <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6338,19 +6338,19 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>S7-R21</t>
+          <t>S7-R20</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6405,354 +6405,354 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>28509</t>
+          <t>28508</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>FD-TMPL-008</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — delete</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>S7-R21</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>28509</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
           <t>FD-TMPL-009</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>S7-N1, S7-R4</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>28510</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>FD-TMPL-010</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>S2-R14, S2-R15, S2-R16, S5-R10</t>
         </is>
       </c>
-      <c r="K90" s="3" t="inlineStr">
+      <c r="K91" s="3" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="L90" s="3" t="inlineStr">
+      <c r="L91" s="3" t="inlineStr">
         <is>
           <t>28511</t>
         </is>
       </c>
-      <c r="M90" s="3" t="inlineStr">
+      <c r="M91" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-011</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>S7-R12e, S7-R14, §5-R6</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>28512</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>FD-TMPL-012</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>Environment window — shared env: cannot empty the location's template library (real templates in use).</t>
         </is>
       </c>
-      <c r="J92" s="6" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>S7-R11</t>
         </is>
       </c>
-      <c r="K92" s="6" t="inlineStr">
+      <c r="K93" s="5" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="L92" s="6" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>28513</t>
         </is>
       </c>
-      <c r="M92" s="6" t="inlineStr">
+      <c r="M93" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-013</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — validation</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>S7-R3, §5-R2</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>28514</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>S7-R2, S7-R13, S7-R15</t>
+          <t>S7-R3, §5-R2</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -6807,19 +6807,19 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>28514</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>S7-R19</t>
+          <t>S7-R2, S7-R13, S7-R15</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -6874,19 +6874,19 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>S13-R8, S7-R7b</t>
+          <t>S7-R19</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -6941,354 +6941,354 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>28517</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>FD-TMPL-016</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — permissions</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>S13-R8, S7-R7b</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>28517</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
           <t>FD-TMPL-017</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>S7-R12c</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>28518</t>
         </is>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>FD-PROC-001</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — template builder</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — Processing-Fee builder UI (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>S8-R1, S8-R3, S7-R12a</t>
         </is>
       </c>
-      <c r="K98" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — Processing-Fee builder UI (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>28519</t>
         </is>
       </c>
-      <c r="M98" s="5" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>FD-PROC-002</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — methods</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — Processing-Fee builder UI (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
         </is>
       </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — Processing-Fee builder UI (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>28520</t>
         </is>
       </c>
-      <c r="M99" s="5" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>FD-PROC-003</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — Processing-Fee builder UI (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>S8-R10, S8-N3, S7-R12e</t>
         </is>
       </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — Processing-Fee builder UI (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>28521</t>
         </is>
       </c>
-      <c r="M100" s="5" t="inlineStr">
+      <c r="M101" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>FD-PROC-004</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Processing Fee — taxable + jurisdiction note</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — Processing-Fee builder UI (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — Processing-Fee builder UI (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
-        <is>
-          <t>28522</t>
-        </is>
-      </c>
-      <c r="M101" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PROC-004</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>S8-R16, S8-N1, S8-N2</t>
+          <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7343,19 +7343,19 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>S8-R14, S7-R5</t>
+          <t>S8-R16, S8-N1, S8-N2</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -7410,287 +7410,287 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>28524</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>FD-PROC-006</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Processing Fee — auto-apply</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>S8-R14, S7-R5</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>28524</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
           <t>FD-PROC-007</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — customer default</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>S8-R15, S9-R2</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>28525</t>
         </is>
       </c>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="M105" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>FD-PROC-008</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>Processing Fee — WO behavior</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>S8-R17, S8-N5, S3-R9</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>28526</t>
-        </is>
-      </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
+          <t>FD-PROC-008</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Processing Fee — WO behavior</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>S8-R17, S8-N5, S3-R9</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>case-update</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>28526</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
           <t>FD-PROC-009</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
-      <c r="I106" s="3" t="inlineStr">
+      <c r="I107" s="3" t="inlineStr">
         <is>
           <t>Dev fix — FDBUG-2 — processing-fee Grand-Total base wrongly includes whole-WO fees + their tax.</t>
         </is>
       </c>
-      <c r="J106" s="3" t="inlineStr">
+      <c r="J107" s="3" t="inlineStr">
         <is>
           <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
         </is>
       </c>
-      <c r="K106" s="3" t="inlineStr">
+      <c r="K107" s="3" t="inlineStr">
         <is>
           <t>code-bug</t>
         </is>
       </c>
-      <c r="L106" s="3" t="inlineStr">
+      <c r="L107" s="3" t="inlineStr">
         <is>
           <t>28527</t>
         </is>
       </c>
-      <c r="M106" s="3" t="inlineStr">
+      <c r="M107" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>FD-PROC-010</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>API — Processing Fee — negative</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>S8-N4</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>28528</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>API — Processing Fee — negative</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>S8-R2</t>
+          <t>S8-N4</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -7745,19 +7745,19 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>28528</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>S8-R18, S8-R19</t>
+          <t>S8-R2</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -7812,19 +7812,19 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>28529</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>§5-R4 (multiple Processing Fees)</t>
+          <t>S8-R18, S8-R19</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -7879,19 +7879,19 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>S8-N6</t>
+          <t>§5-R4 (multiple Processing Fees)</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -7946,19 +7946,19 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>28532</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-001</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>S5-R1</t>
+          <t>S8-N6</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8013,19 +8013,19 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-002</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
+          <t>S5-R1</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8080,19 +8080,19 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-003</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>S5-R2, S5-R3</t>
+          <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8147,19 +8147,19 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>28535</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-004</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Customer document — amount format</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>S5-R4, S5-R9, S12-R7</t>
+          <t>S5-R2, S5-R3</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8214,19 +8214,19 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-005</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>S5-R5, S5-R6</t>
+          <t>S5-R4, S5-R9, S12-R7</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8281,19 +8281,19 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>28536</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-006</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>S5-R7, S5-R8</t>
+          <t>S5-R5, S5-R6</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -8348,19 +8348,19 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-007</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>S5-R6, S8-R22</t>
+          <t>S5-R7, S5-R8</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -8415,19 +8415,19 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-008</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>S14-R1</t>
+          <t>S5-R6, S8-R22</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -8482,19 +8482,19 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-009</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>S14-R2</t>
+          <t>S14-R1</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -8549,19 +8549,19 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>28541</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-010</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>§5-R12</t>
+          <t>S14-R2</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -8616,1225 +8616,1225 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>28541</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>FD-DOC-010</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Customer document — line-level $0 target</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>§5-R12</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>28542</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
           <t>FD-DOC-011</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>Customer document — layout</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>S5-R5</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
         <is>
           <t>28543</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="M123" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>FD-QB-001</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="I124" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J123" s="6" t="inlineStr">
+      <c r="J124" s="5" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
       </c>
-      <c r="K123" s="6" t="inlineStr">
+      <c r="K124" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L123" s="6" t="inlineStr">
+      <c r="L124" s="5" t="inlineStr">
         <is>
           <t>28544</t>
         </is>
       </c>
-      <c r="M123" s="6" t="inlineStr">
+      <c r="M124" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>FD-QB-002</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
+      <c r="I125" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J124" s="6" t="inlineStr">
+      <c r="J125" s="5" t="inlineStr">
         <is>
           <t>S6-R3, S6-R5</t>
         </is>
       </c>
-      <c r="K124" s="6" t="inlineStr">
+      <c r="K125" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L124" s="6" t="inlineStr">
+      <c r="L125" s="5" t="inlineStr">
         <is>
           <t>28545</t>
         </is>
       </c>
-      <c r="M124" s="6" t="inlineStr">
+      <c r="M125" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>FD-QB-003</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>QuickBooks sync — edge</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E126" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G125" s="6" t="inlineStr">
+      <c r="G126" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="H126" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J125" s="6" t="inlineStr">
+      <c r="J126" s="5" t="inlineStr">
         <is>
           <t>S6-R1, §5-R8</t>
         </is>
       </c>
-      <c r="K125" s="6" t="inlineStr">
+      <c r="K126" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L125" s="6" t="inlineStr">
+      <c r="L126" s="5" t="inlineStr">
         <is>
           <t>28546</t>
         </is>
       </c>
-      <c r="M125" s="6" t="inlineStr">
+      <c r="M126" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>FD-QB-004</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G126" s="6" t="inlineStr">
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H126" s="6" t="inlineStr">
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I126" s="6" t="inlineStr">
+      <c r="I127" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J126" s="6" t="inlineStr">
+      <c r="J127" s="5" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6a, S6-R6d</t>
         </is>
       </c>
-      <c r="K126" s="6" t="inlineStr">
+      <c r="K127" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L126" s="6" t="inlineStr">
+      <c r="L127" s="5" t="inlineStr">
         <is>
           <t>28547</t>
         </is>
       </c>
-      <c r="M126" s="6" t="inlineStr">
+      <c r="M127" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>FD-QB-005</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E128" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G127" s="6" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="H128" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J127" s="6" t="inlineStr">
+      <c r="J128" s="5" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6d</t>
         </is>
       </c>
-      <c r="K127" s="6" t="inlineStr">
+      <c r="K128" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L127" s="6" t="inlineStr">
+      <c r="L128" s="5" t="inlineStr">
         <is>
           <t>28548</t>
         </is>
       </c>
-      <c r="M127" s="6" t="inlineStr">
+      <c r="M128" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>FD-QB-006</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G128" s="6" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H128" s="6" t="inlineStr">
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I128" s="6" t="inlineStr">
+      <c r="I129" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J128" s="6" t="inlineStr">
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>S6-R6a</t>
         </is>
       </c>
-      <c r="K128" s="6" t="inlineStr">
+      <c r="K129" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L128" s="6" t="inlineStr">
+      <c r="L129" s="5" t="inlineStr">
         <is>
           <t>28549</t>
         </is>
       </c>
-      <c r="M128" s="6" t="inlineStr">
+      <c r="M129" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>FD-QB-007</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E130" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
+      <c r="F130" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G129" s="6" t="inlineStr">
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H129" s="6" t="inlineStr">
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I129" s="6" t="inlineStr">
+      <c r="I130" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J129" s="6" t="inlineStr">
+      <c r="J130" s="5" t="inlineStr">
         <is>
           <t>S6-R6b</t>
         </is>
       </c>
-      <c r="K129" s="6" t="inlineStr">
+      <c r="K130" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L129" s="6" t="inlineStr">
+      <c r="L130" s="5" t="inlineStr">
         <is>
           <t>28550</t>
         </is>
       </c>
-      <c r="M129" s="6" t="inlineStr">
+      <c r="M130" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>FD-QB-008</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B131" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E131" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F130" s="6" t="inlineStr">
+      <c r="F131" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G130" s="6" t="inlineStr">
+      <c r="G131" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H130" s="6" t="inlineStr">
+      <c r="H131" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I130" s="6" t="inlineStr">
+      <c r="I131" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J130" s="6" t="inlineStr">
+      <c r="J131" s="5" t="inlineStr">
         <is>
           <t>S6-R6c</t>
         </is>
       </c>
-      <c r="K130" s="6" t="inlineStr">
+      <c r="K131" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L130" s="6" t="inlineStr">
+      <c r="L131" s="5" t="inlineStr">
         <is>
           <t>28551</t>
         </is>
       </c>
-      <c r="M130" s="6" t="inlineStr">
+      <c r="M131" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>FD-QB-009</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
+      <c r="F132" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H131" s="6" t="inlineStr">
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I131" s="6" t="inlineStr">
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J131" s="6" t="inlineStr">
+      <c r="J132" s="5" t="inlineStr">
         <is>
           <t>S6-R7, S6-R7a</t>
         </is>
       </c>
-      <c r="K131" s="6" t="inlineStr">
+      <c r="K132" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L131" s="6" t="inlineStr">
+      <c r="L132" s="5" t="inlineStr">
         <is>
           <t>28552</t>
         </is>
       </c>
-      <c r="M131" s="6" t="inlineStr">
+      <c r="M132" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>FD-QB-010</t>
         </is>
       </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — Class</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G132" s="6" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H132" s="6" t="inlineStr">
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J132" s="6" t="inlineStr">
+      <c r="J133" s="5" t="inlineStr">
         <is>
           <t>S6-R8</t>
         </is>
       </c>
-      <c r="K132" s="6" t="inlineStr">
+      <c r="K133" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L132" s="6" t="inlineStr">
+      <c r="L133" s="5" t="inlineStr">
         <is>
           <t>28553</t>
         </is>
       </c>
-      <c r="M132" s="6" t="inlineStr">
+      <c r="M133" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>FD-QB-011</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — Class validation</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G133" s="6" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J133" s="6" t="inlineStr">
+      <c r="J134" s="5" t="inlineStr">
         <is>
           <t>S6-R9</t>
         </is>
       </c>
-      <c r="K133" s="6" t="inlineStr">
+      <c r="K134" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L133" s="6" t="inlineStr">
+      <c r="L134" s="5" t="inlineStr">
         <is>
           <t>28554</t>
         </is>
       </c>
-      <c r="M133" s="6" t="inlineStr">
+      <c r="M134" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>FD-QB-012</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
         <is>
           <t>28555</t>
         </is>
       </c>
-      <c r="M134" s="2" t="inlineStr">
+      <c r="M135" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>FD-QB-013</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G135" s="6" t="inlineStr">
+      <c r="G136" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J135" s="6" t="inlineStr">
+      <c r="J136" s="5" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="K135" s="6" t="inlineStr">
+      <c r="K136" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L135" s="6" t="inlineStr">
+      <c r="L136" s="5" t="inlineStr">
         <is>
           <t>28556</t>
         </is>
       </c>
-      <c r="M135" s="6" t="inlineStr">
+      <c r="M136" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>FD-QB-014</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
         <is>
           <t>28557</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="M137" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>FD-QB-015</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B138" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C138" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E138" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F138" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
+      <c r="G138" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H137" s="6" t="inlineStr">
+      <c r="H138" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I137" s="6" t="inlineStr">
+      <c r="I138" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J137" s="6" t="inlineStr">
+      <c r="J138" s="5" t="inlineStr">
         <is>
           <t>S6-R11, S6-R13</t>
         </is>
       </c>
-      <c r="K137" s="6" t="inlineStr">
+      <c r="K138" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L137" s="6" t="inlineStr">
+      <c r="L138" s="5" t="inlineStr">
         <is>
           <t>28558</t>
         </is>
       </c>
-      <c r="M137" s="6" t="inlineStr">
+      <c r="M138" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="6" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>FD-QB-016</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>QuickBooks sync — tax</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G138" s="6" t="inlineStr">
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="H139" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I138" s="6" t="inlineStr">
+      <c r="I139" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J138" s="6" t="inlineStr">
+      <c r="J139" s="5" t="inlineStr">
         <is>
           <t>S6-R2, §5-R11</t>
         </is>
       </c>
-      <c r="K138" s="6" t="inlineStr">
+      <c r="K139" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L138" s="6" t="inlineStr">
+      <c r="L139" s="5" t="inlineStr">
         <is>
           <t>28559</t>
         </is>
       </c>
-      <c r="M138" s="6" t="inlineStr">
+      <c r="M139" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-001</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Audit log</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="inlineStr">
-        <is>
-          <t>28560</t>
-        </is>
-      </c>
-      <c r="M139" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-002</t>
+          <t>FD-HIST-001</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
+          <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -9889,220 +9889,220 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>28561</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>FD-HIST-002</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>28561</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
           <t>FD-HIST-003</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>S10-R3, S10-R5</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
         <is>
           <t>28562</t>
         </is>
       </c>
-      <c r="M141" s="2" t="inlineStr">
+      <c r="M142" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>FD-HIST-004</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B143" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr">
         <is>
           <t>Audit log — visibility</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr">
+      <c r="F143" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G142" s="6" t="inlineStr">
+      <c r="G143" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="H143" s="5" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I142" s="6" t="inlineStr">
+      <c r="I143" s="5" t="inlineStr">
         <is>
           <t>Environment window — flag-off history visibility (org flag toggle skipped on shared env).</t>
         </is>
       </c>
-      <c r="J142" s="6" t="inlineStr">
+      <c r="J143" s="5" t="inlineStr">
         <is>
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="K142" s="6" t="inlineStr">
+      <c r="K143" s="5" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="L142" s="6" t="inlineStr">
+      <c r="L143" s="5" t="inlineStr">
         <is>
           <t>28563</t>
         </is>
       </c>
-      <c r="M142" s="6" t="inlineStr">
+      <c r="M143" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-005</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Audit log — visibility</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>S10-R1, S10-R6c, S13-R10</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>28564</t>
-        </is>
-      </c>
-      <c r="M143" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-006</t>
+          <t>FD-HIST-005</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Audit log — permission</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>S13-R10</t>
+          <t>S10-R1, S10-R6c, S13-R10</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -10157,19 +10157,19 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>28564</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-007</t>
+          <t>FD-HIST-006</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Audit log — Processing Fee</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
+          <t>S13-R10</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -10224,19 +10224,19 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-008</t>
+          <t>FD-HIST-007</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Audit log — edit entry</t>
+          <t>Audit log — Processing Fee</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>S10-R6c, S2-R6</t>
+          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -10291,34 +10291,34 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-001</t>
+          <t>FD-HIST-008</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>C (Calc/Perms/Validation)</t>
+          <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Calculation contract</t>
+          <t>Audit log — edit entry</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>§5-R3</t>
+          <t>S10-R6c, S2-R6</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -10358,34 +10358,34 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28568</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-002</t>
+          <t>FD-TMPL-018</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>C (Calc/Perms/Validation)</t>
+          <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Calculation contract</t>
+          <t>Template admin — jurisdiction note</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>§5-R3</t>
+          <t>S7-R12f / §5-R15</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -10425,19 +10425,19 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>28569</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28569</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-003</t>
+          <t>FD-CALC-001</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
+          <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>§5-R14</t>
+          <t>§5-R3</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -10492,19 +10492,19 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28570</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28568</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-004</t>
+          <t>FD-CALC-002</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
+          <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>§5-R14</t>
+          <t>§5-R3</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -10559,19 +10559,19 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28571</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28569</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-005</t>
+          <t>FD-CALC-003</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
+          <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>§5-R2</t>
+          <t>§5-R14</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -10626,19 +10626,19 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>28570</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28572</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28570</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-006</t>
+          <t>FD-CALC-004</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
+          <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>§5-R1</t>
+          <t>§5-R14</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -10693,19 +10693,19 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28573</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28571</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-007</t>
+          <t>FD-CALC-005</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
+          <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>§5-R6</t>
+          <t>§5-R2</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -10760,19 +10760,19 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28574</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28572</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-008</t>
+          <t>FD-CALC-006</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
+          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>§5-R6</t>
+          <t>§5-R1</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -10827,19 +10827,19 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28575</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28573</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-009</t>
+          <t>FD-CALC-007</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
+          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>§5-R8</t>
+          <t>§5-R6</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -10894,19 +10894,19 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28576</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28574</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-010</t>
+          <t>FD-CALC-008</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
+          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>§5-R3, §5-R4</t>
+          <t>§5-R6</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -10961,19 +10961,19 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28577</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28575</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-011</t>
+          <t>FD-CALC-009</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
+          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>§5-R11</t>
+          <t>§5-R8</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11028,19 +11028,19 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28578</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28576</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-012</t>
+          <t>FD-CALC-010</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
+          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>§5-R5</t>
+          <t>§5-R3, §5-R4</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -11095,86 +11095,86 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>28579</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28579</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28577</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>FD-CALC-013</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-011</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F159" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G159" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-2 — processing-fee base includes whole-WO adjustments.</t>
-        </is>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>§5-R4, §5-R5</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>28580</t>
-        </is>
-      </c>
-      <c r="M159" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>§5-R11</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>28578</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28578</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-014</t>
+          <t>FD-CALC-012</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
+          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>§5-R4, S8-R10</t>
+          <t>§5-R5</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -11229,86 +11229,86 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>28579</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28579</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>FD-CALC-015</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>FD-CALC-013</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
-        </is>
-      </c>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>28582</t>
-        </is>
-      </c>
-      <c r="M161" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>Dev team</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>Dev fix — FDBUG-2 — processing-fee base includes whole-WO adjustments.</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>§5-R4, §5-R5</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>code-bug</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>28580</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-016</t>
+          <t>FD-CALC-014</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>S6-R10c</t>
+          <t>§5-R4, S8-R10</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -11363,86 +11363,86 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>FD-CALC-017</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-015</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED — ENV</t>
-        </is>
-      </c>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>QA env</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
-        <is>
-          <t>Environment window — environment limitation on the shared qb env.</t>
-        </is>
-      </c>
-      <c r="J163" s="6" t="inlineStr">
-        <is>
-          <t>S6-R10d</t>
-        </is>
-      </c>
-      <c r="K163" s="6" t="inlineStr">
-        <is>
-          <t>flag-off/env</t>
-        </is>
-      </c>
-      <c r="L163" s="6" t="inlineStr">
-        <is>
-          <t>28584</t>
-        </is>
-      </c>
-      <c r="M163" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28584</t>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>28582</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-CALC-016</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -11452,12 +11452,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>S13-R2, S13-N1</t>
+          <t>S6-R10c</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -11497,86 +11497,86 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>28585</t>
+          <t>28583</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>FD-PERM-002</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>FD-CALC-017</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner / Dev ruling</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>PO ruling — Whole-WO adjustment add/edit/remove is FE-only at the BE (tech got 201) (BUG-FD-3). PO/dev: should whole-WO writes be BE-enforced for V1?</t>
-        </is>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>S13-R3</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>PO-question</t>
-        </is>
-      </c>
-      <c r="L165" s="3" t="inlineStr">
-        <is>
-          <t>28586</t>
-        </is>
-      </c>
-      <c r="M165" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>Environment window — environment limitation on the shared qb env.</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>S6-R10d</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L165" s="5" t="inlineStr">
+        <is>
+          <t>28584</t>
+        </is>
+      </c>
+      <c r="M165" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28584</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>S13-R4</t>
+          <t>S13-R2, S13-N1</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -11631,86 +11631,86 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>FD-PERM-004</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>FD-PERM-002</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-NotBuilt</t>
-        </is>
-      </c>
-      <c r="F167" s="5" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G167" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I167" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 11 — Part Sales fees/discounts (SV-73xx); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="J167" s="5" t="inlineStr">
-        <is>
-          <t>S13-R5</t>
-        </is>
-      </c>
-      <c r="K167" s="5" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="L167" s="5" t="inlineStr">
-        <is>
-          <t>28588</t>
-        </is>
-      </c>
-      <c r="M167" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>Product Owner / Dev ruling</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>PO ruling — Whole-WO adjustment add/edit/remove is FE-only at the BE (tech got 201) (BUG-FD-3). PO/dev: should whole-WO writes be BE-enforced for V1?</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>S13-R3</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>PO-question</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>28586</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>S13-R6</t>
+          <t>S13-R4</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -11765,19 +11765,19 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>28589</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PERM-004</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>S13-R7</t>
+          <t>S13-R5</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -11832,19 +11832,19 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>28588</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>S13-R8</t>
+          <t>S13-R6</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -11899,19 +11899,19 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>28591</t>
+          <t>28589</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>S13-R9, S13-N3</t>
+          <t>S13-R7</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -11966,19 +11966,19 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>28592</t>
+          <t>28590</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>S13-R10</t>
+          <t>S13-R8</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -12033,19 +12033,19 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>S13-R1, feature flag + permission (both gates)</t>
+          <t>S13-R9, S13-N3</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -12100,421 +12100,421 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
+          <t>FD-PERM-009</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>S13-R10</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>28593</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>FD-PERM-010</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>S13-R1, feature flag + permission (both gates)</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>28594</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
           <t>FD-PERM-011</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>S1-N1, S3-R1b, S3-R1a</t>
         </is>
       </c>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L174" s="2" t="inlineStr">
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
         <is>
           <t>28595</t>
         </is>
       </c>
-      <c r="M174" s="2" t="inlineStr">
+      <c r="M176" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>FD-FLAG-001</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr">
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
+      <c r="C177" s="5" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E177" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr">
+      <c r="F177" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G175" s="6" t="inlineStr">
+      <c r="G177" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H175" s="6" t="inlineStr">
+      <c r="H177" s="5" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I175" s="6" t="inlineStr">
+      <c r="I177" s="5" t="inlineStr">
         <is>
           <t>Environment window — flag-off window (org-level FeesAndDiscounts toggle skipped on shared env).</t>
         </is>
       </c>
-      <c r="J175" s="6" t="inlineStr">
+      <c r="J177" s="5" t="inlineStr">
         <is>
           <t>§1 feature flag, S13-R1</t>
         </is>
       </c>
-      <c r="K175" s="6" t="inlineStr">
+      <c r="K177" s="5" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="L175" s="6" t="inlineStr">
+      <c r="L177" s="5" t="inlineStr">
         <is>
           <t>28596</t>
         </is>
       </c>
-      <c r="M175" s="6" t="inlineStr">
+      <c r="M177" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28596</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="6" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>FD-FLAG-002</t>
         </is>
       </c>
-      <c r="B176" s="6" t="inlineStr">
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G176" s="6" t="inlineStr">
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H176" s="6" t="inlineStr">
+      <c r="H178" s="5" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I176" s="6" t="inlineStr">
+      <c r="I178" s="5" t="inlineStr">
         <is>
           <t>Environment window — flag-off exception (history log visible with flag off).</t>
         </is>
       </c>
-      <c r="J176" s="6" t="inlineStr">
+      <c r="J178" s="5" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="K176" s="6" t="inlineStr">
+      <c r="K178" s="5" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="L176" s="6" t="inlineStr">
+      <c r="L178" s="5" t="inlineStr">
         <is>
           <t>28597</t>
         </is>
       </c>
-      <c r="M176" s="6" t="inlineStr">
+      <c r="M178" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="6" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>FD-FLAG-003</t>
         </is>
       </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="B179" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E179" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
+      <c r="F179" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G177" s="6" t="inlineStr">
+      <c r="G179" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="H179" s="5" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="I177" s="6" t="inlineStr">
+      <c r="I179" s="5" t="inlineStr">
         <is>
           <t>Environment window — flag ON + permission-required interaction (flag-side complement).</t>
         </is>
       </c>
-      <c r="J177" s="6" t="inlineStr">
+      <c r="J179" s="5" t="inlineStr">
         <is>
           <t>§1 feature flag + S13-R1</t>
         </is>
       </c>
-      <c r="K177" s="6" t="inlineStr">
+      <c r="K179" s="5" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="L177" s="6" t="inlineStr">
+      <c r="L179" s="5" t="inlineStr">
         <is>
           <t>28598</t>
         </is>
       </c>
-      <c r="M177" s="6" t="inlineStr">
+      <c r="M179" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>FD-VAL-001</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G178" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I178" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J178" s="3" t="inlineStr">
-        <is>
-          <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L178" s="3" t="inlineStr">
-        <is>
-          <t>28599</t>
-        </is>
-      </c>
-      <c r="M178" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>FD-VAL-002</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr">
-        <is>
-          <t>S2-N2, §5-R1</t>
-        </is>
-      </c>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L179" s="2" t="inlineStr">
-        <is>
-          <t>28600</t>
-        </is>
-      </c>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>S2-N1, S2-R19</t>
+          <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -12569,19 +12569,19 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>§5-R2</t>
+          <t>S2-N2, §5-R1</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -12636,19 +12636,19 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>§5-R1</t>
+          <t>S2-N1, S2-R19</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -12703,19 +12703,19 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>§5-R6, S2-R24, S2-R25</t>
+          <t>§5-R2</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -12770,77 +12770,211 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
+          <t>FD-VAL-005</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>§5-R1</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>28603</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-006</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>§5-R6, S2-R24, S2-R25</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>28604</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
           <t>FD-VAL-007</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>Verified, but Double-add (BUG-FD-1) not reproduced — PO to confirm fixed.</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr">
         <is>
           <t>verified (PO-confirm)</t>
         </is>
       </c>
-      <c r="L184" s="2" t="inlineStr">
+      <c r="L186" s="2" t="inlineStr">
         <is>
           <t>28605</t>
         </is>
       </c>
-      <c r="M184" s="2" t="inlineStr">
+      <c r="M186" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
@@ -12857,7 +12991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -12866,47 +13000,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Fees &amp; Discounts V1 — Blockers Tracker · Summary</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n"/>
-      <c r="C1" s="8" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Total authored cases</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C3" s="8" t="n"/>
+      <c r="B3" s="7" t="n">
+        <v>185</v>
+      </c>
+      <c r="C3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
@@ -12919,7 +13053,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12934,7 +13068,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -12943,30 +13077,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>BLOCKED — DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Dev team (Stories 8 &amp; 11)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env (QuickBooks, flag-off)</t>
         </is>
@@ -13009,14 +13143,14 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>183</v>
-      </c>
-      <c r="C12" s="8" t="inlineStr"/>
+        <v>185</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -13029,45 +13163,45 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n"/>
+      <c r="C14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="C15" s="8" t="n"/>
+      <c r="B15" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="C16" s="8" t="n"/>
+      <c r="B16" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="C16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="C17" s="8" t="n"/>
+      <c r="C17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -13080,45 +13214,45 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n"/>
+      <c r="C19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>code-bug</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="8" t="n"/>
+      <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>PO-question</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="8" t="n"/>
+      <c r="C21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C22" s="8" t="n"/>
+      <c r="B22" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -13131,161 +13265,139 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Story 11 — Part Sales fees/discounts (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8" t="n"/>
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Story 8 — Processing-Fee builder UI (SV-73xx)</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="8" t="n"/>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>ENV — by sub-bucket</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>quickbooks</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>ENV — by sub-bucket</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>quickbooks</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C29" s="8" t="n"/>
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>flag-off/env</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" s="8" t="n"/>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• Fresh qb QA cookies (admin; tech quick-login is FLAKY — retest each run)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>• Dev deploys Story 8 (Processing-Fee builder UI) + Story 11 (Part Sales fees/discounts)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>unblocks the 0 DEV-NOT-BUILT cases (Story 8 = 0, Story 11 = 0); then QA re-runs VIU.</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>• Fresh qb QA cookies (admin; tech quick-login is FLAKY — retest each run)</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n"/>
+          <t>• A QuickBooks-connected env (or dev/QB-side inspection) for Story 6</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>unblocks the 14 QuickBooks ENV cases (mapping guard, sync, negative-total credit memo).</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>• Dev deploys Story 8 (Processing-Fee builder UI) + Story 11 (Part Sales fees/discounts)</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>unblocks the 12 DEV-NOT-BUILT cases (Story 8 = 4, Story 11 = 8); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
+          <t>• A flag-off maintenance window on a non-shared env</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>unblocks the 6 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>• A QuickBooks-connected env (or dev/QB-side inspection) for Story 6</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>unblocks the 14 QuickBooks ENV cases (mapping guard, sync, negative-total credit memo).</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n"/>
+          <t>• PO/dev rulings on the deviations + double-add + NOTE-FD-4</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 7 copy/UX-drift deviations once the build is confirmed intended.</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>• A flag-off maintenance window on a non-shared env</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>unblocks the 6 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>• PO/dev rulings on the deviations + double-add + NOTE-FD-4</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 10 copy/UX-drift deviations once the build is confirmed intended.</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
           <t>• Restricted-role accounts (or confirmation the self-service staff role-switch is usable on qb)</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>unblocks the 0 NEEDS-ACCOUNT Story-13 per-role negatives (restore Tech afterward).</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n"/>
+      <c r="C36" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5814,7 +5814,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-016</t>
+          <t>FD-CUST-017</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults — known bug</t>
+          <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5854,34 +5854,34 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Verified, but Double-add (BUG-FD-1) did NOT reproduce on batch-2 (backend dedupes) — PO to confirm the S9 fix shipped; re-scope to single adjustment.</t>
+          <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>S9 known gap (§14 item 4)</t>
+          <t>S9-N1</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>verified (PO-confirm)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-017</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>API — Customer Fees &amp; Discounts tab — negative</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>S9-N1</t>
+          <t>S7-R7a, S7-R7c</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5936,19 +5936,19 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>28501</t>
+          <t>28502</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>S7-R7a, S7-R7c</t>
+          <t>S7-R8, S12-R8</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6003,19 +6003,19 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>S7-R8, S12-R8</t>
+          <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6070,19 +6070,19 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>28504</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
+          <t>S7-R12a, S7-R18a</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6137,19 +6137,19 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>28504</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>S7-R12a, S7-R18a</t>
+          <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6204,19 +6204,19 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28506</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
+          <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6271,19 +6271,19 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
+          <t>S7-R20</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6338,19 +6338,19 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>28508</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>S7-R20</t>
+          <t>S7-R21</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6405,19 +6405,19 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>S7-R21</t>
+          <t>S7-N1, S7-R4</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6472,287 +6472,287 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>28509</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-009</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>FD-TMPL-010</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — delete</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>S7-N1, S7-R4</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>28510</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Template admin — scoping</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>S2-R14, S2-R15, S2-R16, S5-R10</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>case-update</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>28511</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>FD-TMPL-010</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>FD-TMPL-011</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>Template admin — scoping</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — dialog fields</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>S7-R12e, S7-R14, §5-R6</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>28512</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>FD-TMPL-012</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Template admin — list</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Verify the template list empty-state message</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>S2-R14, S2-R15, S2-R16, S5-R10</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
-        <is>
-          <t>28511</t>
-        </is>
-      </c>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-011</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Environment window — shared env: cannot empty the location's template library (real templates in use).</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>S7-R11</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>28513</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>FD-TMPL-013</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — dialog fields</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>S7-R12e, S7-R14, §5-R6</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>28512</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>FD-TMPL-012</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Template admin — list</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Verify the template list empty-state message</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — ENV</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>QA env</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Environment window — shared env: cannot empty the location's template library (real templates in use).</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>S7-R11</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="inlineStr">
-        <is>
-          <t>flag-off/env</t>
-        </is>
-      </c>
-      <c r="L93" s="5" t="inlineStr">
-        <is>
-          <t>28513</t>
-        </is>
-      </c>
-      <c r="M93" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — validation</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>S7-R3, §5-R2</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>28514</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>S7-R3, §5-R2</t>
+          <t>S7-R2, S7-R13, S7-R15</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -6807,19 +6807,19 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>S7-R2, S7-R13, S7-R15</t>
+          <t>S7-R19</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -6874,19 +6874,19 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>S7-R19</t>
+          <t>S13-R8, S7-R7b</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -6941,19 +6941,19 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>S13-R8, S7-R7b</t>
+          <t>S7-R12c</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7008,19 +7008,19 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>28517</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-PROC-001</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Processing Fee — template builder</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>S7-R12c</t>
+          <t>S8-R1, S8-R3, S7-R12a</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-001</t>
+          <t>FD-PROC-002</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -7097,12 +7097,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template builder</t>
+          <t>Processing Fee — methods</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>S8-R1, S8-R3, S7-R12a</t>
+          <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7142,19 +7142,19 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-002</t>
+          <t>FD-PROC-003</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — methods</t>
+          <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
+          <t>S8-R10, S8-N3, S7-R12e</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7209,19 +7209,19 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-003</t>
+          <t>FD-PROC-004</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no Max Amount</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>S8-R10, S8-N3, S7-R12e</t>
+          <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7276,19 +7276,19 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-004</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — taxable + jurisdiction note</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
+          <t>S8-R16, S8-N1, S8-N2</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7343,19 +7343,19 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>S8-R16, S8-N1, S8-N2</t>
+          <t>S8-R14, S7-R5</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -7410,19 +7410,19 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>S8-R14, S7-R5</t>
+          <t>S8-R15, S9-R2</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -7477,86 +7477,86 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>28524</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>FD-PROC-007</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>FD-PROC-008</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — customer default</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>S8-R15, S9-R2</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>28525</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Processing Fee — WO behavior</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>S8-R17, S8-N5, S3-R9</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>case-update</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>28526</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>FD-PROC-008</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -7591,106 +7591,106 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>QA (case-text update)</t>
+          <t>Dev team</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+          <t>Dev fix — FDBUG-2 — processing-fee Grand-Total base wrongly includes whole-WO fees + their tax.</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>S8-R17, S8-N5, S3-R9</t>
+          <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>case-update</t>
+          <t>code-bug</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>FD-PROC-009</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>FD-PROC-010</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>Processing Fee — calculation</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-2 — processing-fee Grand-Total base wrongly includes whole-WO fees + their tax.</t>
-        </is>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>28527</t>
-        </is>
-      </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>API — Processing Fee — negative</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>S8-N4</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>28528</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>API — Processing Fee — negative</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>S8-N4</t>
+          <t>S8-R2</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -7745,19 +7745,19 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>28528</t>
+          <t>28529</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>S8-R2</t>
+          <t>S8-R18, S8-R19</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -7812,19 +7812,19 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>S8-R18, S8-R19</t>
+          <t>§5-R4 (multiple Processing Fees)</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -7879,19 +7879,19 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>§5-R4 (multiple Processing Fees)</t>
+          <t>S8-N6</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -7946,19 +7946,19 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>S8-N6</t>
+          <t>S5-R1</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8013,19 +8013,19 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>28532</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-001</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>S5-R1</t>
+          <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8080,19 +8080,19 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-002</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
+          <t>S5-R2, S5-R3</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8147,19 +8147,19 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-003</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>S5-R2, S5-R3</t>
+          <t>S5-R4, S5-R9, S12-R7</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8214,19 +8214,19 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>28535</t>
+          <t>28536</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-004</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Customer document — amount format</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
+          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>S5-R4, S5-R9, S12-R7</t>
+          <t>S5-R5, S5-R6</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8281,19 +8281,19 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-005</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>S5-R5, S5-R6</t>
+          <t>S5-R7, S5-R8</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -8348,19 +8348,19 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-006</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>S5-R7, S5-R8</t>
+          <t>S5-R6, S8-R22</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -8415,19 +8415,19 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-007</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>S5-R6, S8-R22</t>
+          <t>S14-R1</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -8482,19 +8482,19 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-008</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>S14-R1</t>
+          <t>S14-R2</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -8549,19 +8549,19 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>28541</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-009</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>S14-R2</t>
+          <t>§5-R12</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -8616,19 +8616,19 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>28541</t>
+          <t>28542</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-010</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>§5-R12</t>
+          <t>S5-R5</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -8683,86 +8683,86 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>28543</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>FD-DOC-011</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>FD-QB-001</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Customer document — layout</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>S5-R5</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>28543</t>
-        </is>
-      </c>
-      <c r="M123" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>QuickBooks sync</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>Dev / QA env</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>S6-R1</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>quickbooks</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>28544</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-001</t>
+          <t>FD-QB-002</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
+          <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>S6-R1</t>
+          <t>S6-R3, S6-R5</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
@@ -8817,19 +8817,19 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>28544</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-002</t>
+          <t>FD-QB-003</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks sync</t>
+          <t>QuickBooks sync — edge</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
+          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>S6-R3, S6-R5</t>
+          <t>S6-R1, §5-R8</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
@@ -8884,19 +8884,19 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>28546</t>
         </is>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-003</t>
+          <t>FD-QB-004</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks sync — edge</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
+          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>S6-R1, §5-R8</t>
+          <t>S6-R6, S6-R6a, S6-R6d</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -8951,19 +8951,19 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-004</t>
+          <t>FD-QB-005</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
+          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>S6-R6, S6-R6a, S6-R6d</t>
+          <t>S6-R6, S6-R6d</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
@@ -9018,19 +9018,19 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-005</t>
+          <t>FD-QB-006</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard</t>
+          <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
+          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>S6-R6, S6-R6d</t>
+          <t>S6-R6a</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
@@ -9085,19 +9085,19 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-006</t>
+          <t>FD-QB-007</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard scope</t>
+          <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
+          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>S6-R6a</t>
+          <t>S6-R6b</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
@@ -9152,19 +9152,19 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-007</t>
+          <t>FD-QB-008</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard (auto-apply)</t>
+          <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
+          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>S6-R6b</t>
+          <t>S6-R6c</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
@@ -9219,19 +9219,19 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>28550</t>
+          <t>28551</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-008</t>
+          <t>FD-QB-009</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard exceptions</t>
+          <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
+          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>S6-R6c</t>
+          <t>S6-R7, S6-R7a</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
@@ -9286,19 +9286,19 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>28552</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-009</t>
+          <t>FD-QB-010</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks — unmap recovery</t>
+          <t>QuickBooks — Class</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
+          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>S6-R7, S6-R7a</t>
+          <t>S6-R8</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -9353,19 +9353,19 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>28553</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-010</t>
+          <t>FD-QB-011</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -9375,12 +9375,12 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks — Class</t>
+          <t>QuickBooks — Class validation</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
+          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>S6-R8</t>
+          <t>S6-R9</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
@@ -9420,287 +9420,287 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>FD-QB-011</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>FD-QB-012</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>QuickBooks — Class validation</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks — negative totals</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>28555</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>FD-QB-013</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>QuickBooks — negative totals</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J134" s="5" t="inlineStr">
-        <is>
-          <t>S6-R9</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr">
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>S6-R10d</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>28554</t>
-        </is>
-      </c>
-      <c r="M134" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>FD-QB-012</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>28556</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>FD-QB-014</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
-        </is>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>28555</t>
-        </is>
-      </c>
-      <c r="M135" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>FD-QB-013</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>S6-R12</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>28557</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>FD-QB-015</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C137" s="5" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G137" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="H136" s="5" t="inlineStr">
+      <c r="H137" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I137" s="5" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>S6-R10d</t>
-        </is>
-      </c>
-      <c r="K136" s="5" t="inlineStr">
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>S6-R11, S6-R13</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>28556</t>
-        </is>
-      </c>
-      <c r="M136" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>FD-QB-014</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>B (Customer/Admin/Finance)</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks — negative totals</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>S6-R12</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>28557</t>
-        </is>
-      </c>
-      <c r="M137" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>28558</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-015</t>
+          <t>FD-QB-016</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>QuickBooks sync — tax</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
+          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>S6-R11, S6-R13</t>
+          <t>S6-R2, §5-R11</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -9755,86 +9755,86 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>FD-QB-016</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-001</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>QuickBooks sync — tax</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — ENV</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>Dev / QA env</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
-        </is>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>S6-R2, §5-R11</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>quickbooks</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>28559</t>
-        </is>
-      </c>
-      <c r="M139" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>28560</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-001</t>
+          <t>FD-HIST-002</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
+          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -9889,19 +9889,19 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-002</t>
+          <t>FD-HIST-003</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
+          <t>S10-R3, S10-R5</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -9956,153 +9956,153 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>28561</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>FD-HIST-003</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>FD-HIST-004</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Audit log</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>S10-R3, S10-R5</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="inlineStr">
-        <is>
-          <t>28562</t>
-        </is>
-      </c>
-      <c r="M142" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Audit log — visibility</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Environment window — flag-off history visibility (org flag toggle skipped on shared env).</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>S10-R1</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>28563</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>FD-HIST-004</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>FD-HIST-005</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Audit log — visibility</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — ENV</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>QA env</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>Environment window — flag-off history visibility (org flag toggle skipped on shared env).</t>
-        </is>
-      </c>
-      <c r="J143" s="5" t="inlineStr">
-        <is>
-          <t>S10-R1</t>
-        </is>
-      </c>
-      <c r="K143" s="5" t="inlineStr">
-        <is>
-          <t>flag-off/env</t>
-        </is>
-      </c>
-      <c r="L143" s="5" t="inlineStr">
-        <is>
-          <t>28563</t>
-        </is>
-      </c>
-      <c r="M143" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>S10-R1, S10-R6c, S13-R10</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>28564</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-005</t>
+          <t>FD-HIST-006</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Audit log — visibility</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>S10-R1, S10-R6c, S13-R10</t>
+          <t>S13-R10</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -10157,19 +10157,19 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>28564</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-006</t>
+          <t>FD-HIST-007</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Audit log — permission</t>
+          <t>Audit log — Processing Fee</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>S13-R10</t>
+          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -10224,19 +10224,19 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-007</t>
+          <t>FD-HIST-008</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Audit log — Processing Fee</t>
+          <t>Audit log — edit entry</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
+          <t>S10-R6c, S2-R6</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -10291,19 +10291,19 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-008</t>
+          <t>FD-TMPL-018</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Audit log — edit entry</t>
+          <t>Template admin — jurisdiction note</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>S10-R6c, S2-R6</t>
+          <t>S7-R12f / §5-R15</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -10358,34 +10358,34 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-018</t>
+          <t>FD-CALC-001</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>B (Customer/Admin/Finance)</t>
+          <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Template admin — jurisdiction note</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
+          <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>S7-R12f / §5-R15</t>
+          <t>§5-R3</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -10425,19 +10425,19 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28568</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-001</t>
+          <t>FD-CALC-002</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
+          <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -10492,19 +10492,19 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28568</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28569</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-002</t>
+          <t>FD-CALC-003</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
+          <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>§5-R3</t>
+          <t>§5-R14</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -10559,19 +10559,19 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>28569</t>
+          <t>28570</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28569</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28570</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-003</t>
+          <t>FD-CALC-004</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
+          <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -10626,19 +10626,19 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28570</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28571</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-004</t>
+          <t>FD-CALC-005</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
+          <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>§5-R14</t>
+          <t>§5-R2</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -10693,19 +10693,19 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28571</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28572</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-005</t>
+          <t>FD-CALC-006</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
+          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>§5-R2</t>
+          <t>§5-R1</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -10760,19 +10760,19 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28572</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28573</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-006</t>
+          <t>FD-CALC-007</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
+          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>§5-R1</t>
+          <t>§5-R6</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -10827,19 +10827,19 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28573</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28574</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-007</t>
+          <t>FD-CALC-008</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
+          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -10894,19 +10894,19 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28574</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28575</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-008</t>
+          <t>FD-CALC-009</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
+          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>§5-R6</t>
+          <t>§5-R8</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -10961,19 +10961,19 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28575</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28576</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-009</t>
+          <t>FD-CALC-010</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
+          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>§5-R8</t>
+          <t>§5-R3, §5-R4</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11028,19 +11028,19 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28576</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28577</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-010</t>
+          <t>FD-CALC-011</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
+          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>§5-R3, §5-R4</t>
+          <t>§5-R11</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -11095,19 +11095,19 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28577</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28578</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-011</t>
+          <t>FD-CALC-012</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
+          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>§5-R11</t>
+          <t>§5-R5</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -11162,153 +11162,153 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>28579</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28578</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28579</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>FD-CALC-012</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>FD-CALC-013</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>§5-R5</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="inlineStr">
-        <is>
-          <t>28579</t>
-        </is>
-      </c>
-      <c r="M160" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28579</t>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>Dev team</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>Dev fix — FDBUG-2 — processing-fee base includes whole-WO adjustments.</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>§5-R4, §5-R5</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>code-bug</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>28580</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>FD-CALC-013</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-014</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="I161" s="3" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-2 — processing-fee base includes whole-WO adjustments.</t>
-        </is>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>§5-R4, §5-R5</t>
-        </is>
-      </c>
-      <c r="K161" s="3" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="L161" s="3" t="inlineStr">
-        <is>
-          <t>28580</t>
-        </is>
-      </c>
-      <c r="M161" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>§5-R4, S8-R10</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>28581</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-014</t>
+          <t>FD-CALC-015</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
+          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>§5-R4, S8-R10</t>
+          <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -11363,19 +11363,19 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-015</t>
+          <t>FD-CALC-016</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
+          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
+          <t>S6-R10c</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -11430,287 +11430,287 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>28582</t>
+          <t>28583</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>FD-CALC-016</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>FD-CALC-017</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C164" s="5" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>S6-R10c</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="inlineStr">
-        <is>
-          <t>28583</t>
-        </is>
-      </c>
-      <c r="M164" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>Environment window — environment limitation on the shared qb env.</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>S6-R10d</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L164" s="5" t="inlineStr">
+        <is>
+          <t>28584</t>
+        </is>
+      </c>
+      <c r="M164" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28584</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>FD-CALC-017</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>FD-PERM-001</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D165" s="5" t="inlineStr">
-        <is>
-          <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F165" s="5" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>S13-R2, S13-N1</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>28585</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>FD-PERM-002</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G165" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — ENV</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr">
-        <is>
-          <t>QA env</t>
-        </is>
-      </c>
-      <c r="I165" s="5" t="inlineStr">
-        <is>
-          <t>Environment window — environment limitation on the shared qb env.</t>
-        </is>
-      </c>
-      <c r="J165" s="5" t="inlineStr">
-        <is>
-          <t>S6-R10d</t>
-        </is>
-      </c>
-      <c r="K165" s="5" t="inlineStr">
-        <is>
-          <t>flag-off/env</t>
-        </is>
-      </c>
-      <c r="L165" s="5" t="inlineStr">
-        <is>
-          <t>28584</t>
-        </is>
-      </c>
-      <c r="M165" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28584</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>FD-PERM-001</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>Product Owner / Dev ruling</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>PO ruling — Whole-WO adjustment add/edit/remove is FE-only at the BE (tech got 201) (BUG-FD-3). PO/dev: should whole-WO writes be BE-enforced for V1?</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>S13-R3</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>PO-question</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>28586</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>FD-PERM-003</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>S13-R2, S13-N1</t>
-        </is>
-      </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="inlineStr">
-        <is>
-          <t>28585</t>
-        </is>
-      </c>
-      <c r="M166" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>FD-PERM-002</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner / Dev ruling</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>PO ruling — Whole-WO adjustment add/edit/remove is FE-only at the BE (tech got 201) (BUG-FD-3). PO/dev: should whole-WO writes be BE-enforced for V1?</t>
-        </is>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>S13-R3</t>
-        </is>
-      </c>
-      <c r="K167" s="3" t="inlineStr">
-        <is>
-          <t>PO-question</t>
-        </is>
-      </c>
-      <c r="L167" s="3" t="inlineStr">
-        <is>
-          <t>28586</t>
-        </is>
-      </c>
-      <c r="M167" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>S13-R4</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>28587</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PERM-004</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>S13-R4</t>
+          <t>S13-R5</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -11765,19 +11765,19 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>28588</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-004</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>S13-R5</t>
+          <t>S13-R6</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -11832,19 +11832,19 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>28589</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>S13-R6</t>
+          <t>S13-R7</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -11899,19 +11899,19 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>28589</t>
+          <t>28590</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>S13-R7</t>
+          <t>S13-R8</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -11966,19 +11966,19 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>S13-R8</t>
+          <t>S13-R9, S13-N3</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -12033,19 +12033,19 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>28591</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PERM-009</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>S13-R9, S13-N3</t>
+          <t>S13-R10</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -12100,19 +12100,19 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>28592</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>S13-R10</t>
+          <t>S13-R1, feature flag + permission (both gates)</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -12167,19 +12167,19 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>S13-R1, feature flag + permission (both gates)</t>
+          <t>S1-N1, S3-R1b, S3-R1a</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -12234,86 +12234,86 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>FD-PERM-011</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>FD-FLAG-001</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr">
-        <is>
-          <t>S1-N1, S3-R1b, S3-R1a</t>
-        </is>
-      </c>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L176" s="2" t="inlineStr">
-        <is>
-          <t>28595</t>
-        </is>
-      </c>
-      <c r="M176" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Feature-flag gating</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Environment window — flag-off window (org-level FeesAndDiscounts toggle skipped on shared env).</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>§1 feature flag, S13-R1</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L176" s="5" t="inlineStr">
+        <is>
+          <t>28596</t>
+        </is>
+      </c>
+      <c r="M176" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28596</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>FD-FLAG-001</t>
+          <t>FD-FLAG-002</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
+          <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>Environment window — flag-off window (org-level FeesAndDiscounts toggle skipped on shared env).</t>
+          <t>Environment window — flag-off exception (history log visible with flag off).</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>§1 feature flag, S13-R1</t>
+          <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
@@ -12368,19 +12368,19 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28596</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>FD-FLAG-002</t>
+          <t>FD-FLAG-003</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
+          <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>Environment window — flag-off exception (history log visible with flag off).</t>
+          <t>Environment window — flag ON + permission-required interaction (flag-side complement).</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>S10-R1 (flag-off exception)</t>
+          <t>§1 feature flag + S13-R1</t>
         </is>
       </c>
       <c r="K178" s="5" t="inlineStr">
@@ -12435,86 +12435,86 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>FD-FLAG-003</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>FD-VAL-001</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>Feature-flag gating</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
-        <is>
-          <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Blocked-Env</t>
-        </is>
-      </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED — ENV</t>
-        </is>
-      </c>
-      <c r="H179" s="5" t="inlineStr">
-        <is>
-          <t>QA env</t>
-        </is>
-      </c>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>Environment window — flag ON + permission-required interaction (flag-side complement).</t>
-        </is>
-      </c>
-      <c r="J179" s="5" t="inlineStr">
-        <is>
-          <t>§1 feature flag + S13-R1</t>
-        </is>
-      </c>
-      <c r="K179" s="5" t="inlineStr">
-        <is>
-          <t>flag-off/env</t>
-        </is>
-      </c>
-      <c r="L179" s="5" t="inlineStr">
-        <is>
-          <t>28598</t>
-        </is>
-      </c>
-      <c r="M179" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>28599</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-001</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
+          <t>S2-N2, §5-R1</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -12569,19 +12569,19 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>S2-N2, §5-R1</t>
+          <t>S2-N1, S2-R19</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -12636,19 +12636,19 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>S2-N1, S2-R19</t>
+          <t>§5-R2</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -12703,19 +12703,19 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>§5-R2</t>
+          <t>§5-R1</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -12770,19 +12770,19 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>§5-R1</t>
+          <t>§5-R6, S2-R24, S2-R25</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -12837,19 +12837,19 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -12889,92 +12889,25 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>None — VIU-verified; uploadable now.</t>
+          <t>Verified, but Double-add (BUG-FD-1) not reproduced — PO to confirm fixed.</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>§5-R6, S2-R24, S2-R25</t>
+          <t>S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>verified (PO-confirm)</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>FD-VAL-007</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>Verified, but Double-add (BUG-FD-1) not reproduced — PO to confirm fixed.</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2</t>
-        </is>
-      </c>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>verified (PO-confirm)</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr">
-        <is>
-          <t>28605</t>
-        </is>
-      </c>
-      <c r="M186" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
@@ -13020,7 +12953,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C3" s="7" t="n"/>
     </row>
@@ -13053,7 +12986,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -13143,7 +13076,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C12" s="7" t="inlineStr"/>
     </row>
@@ -13183,7 +13116,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" s="7" t="n"/>
     </row>
@@ -13381,7 +13314,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-CUST-016/FD-VAL-007), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 7 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 7 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -1608,7 +1608,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
+          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
+          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
+          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
+          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -1792,67 +1792,67 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>FD-LABOR-003</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Verify the labor fee/discount add entry point is a three-dot menu to the left of the first technician (or 'Unassigned')</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>S1-R2 | SV-8479 (SV-8288 Story 12 — item 1)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>case-update</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>28441</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28441</t>
         </is>
@@ -2998,67 +2998,67 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FD-STATS-001</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner / Dev ruling</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>PO ruling — Stats F&amp;D section is aggregate (Fees/Discounts/Net), not the spec's per-adjustment %+Amount rows (BUG-FD-2/FDBUG-6). PO: is aggregate the intended V1?</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>S4-R1 / S4-R2 / S4-R3 | SV-8479 (SV-8288 Story 12 — item 12)</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>PO-question</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>28459</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
@@ -4807,697 +4807,697 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>FD-WO-017</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED — DEVIATION</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>QA (case-text update)</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement, three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>case-update</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>FD-WO-018</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 2: WO part-row three-dot menu label 'Add Part Fee / Discount')</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>FD-WO-021</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 6: WO Fees &amp; Discounts card disclaimer copy)</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M67" s="4" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>FD-WO-025</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 10: WO toolbar three-dot menu label 'Add Work Order Fee / Discount')</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>FD-WO-028</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Verify the tax-jurisdiction note and the 'Pass convenience fee to customer' banner still appear after the fee/discount UI updates</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — NOTES regression preserve: tax-jurisdiction note in dialogs + 'Pass convenience fee to customer' banner)</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M69" s="4" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>FD-PSALE-002</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 13: remove redundant '+ Add' button in the parts-sale Fees &amp; Discounts column)</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>FD-PSALE-003</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 14: parts-sale per-part three-dot menu label 'Add Part Fee / Discount')</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M71" s="4" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>FD-PSALE-004</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Parts Sale — Fees &amp; Discounts card</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 15: Parts Sale Fees &amp; Discounts card plain-text, no badge, item-5 bracket/sign convention)</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>FD-PSALE-006</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Parts Sale — Financial Info card</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 17: parts-sale Financial Info 'Fees &amp; Discounts (N)' line above Subtotal, hidden when zero)</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M73" s="4" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>FD-PSALE-008</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 19: whole-parts-sale fee/discount modal title 'New Parts Sale Fee / Discount' + new subline 'Applying To: Entire Parts Sale')</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>FD-PSALE-009</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Parts Sale — Statistics tab</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 20: parts-sale Statistics Fees &amp; Discounts section column headings '%' and 'Amount', mirrors item 12)</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M75" s="4" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -12200,445 +12200,445 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>FD-CALC-018</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Verify a work order line total adds the line's own fees to Labor and Parts (Labor $250 + fee +$50.00 + Part $20.00 + fee +$2.20 → line total $322.20)</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>pending-create</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-019</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Verify a discount on a line subtracts from the line total while a fee adds (fees add, discounts subtract in the line total)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>pending-create</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-020</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Verify a line with no fees or discounts shows a line total of Labor + Parts only (unchanged by the fix)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>pending-create</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-021</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Estimate document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>pending-create</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-022</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Invoice document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>pending-create</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>FD-CALC-023</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>C (Calc/Perms/Validation)</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>Verify that when the Fees &amp; Discounts feature is turned off, the line total is Labor + Parts only (gross), with no fee/discount rolled in</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J176" s="4" t="inlineStr">
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED — ENV</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>QA env</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>Environment window — environment limitation on the shared qb env.</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
         <is>
           <t>SV-8480 (S3-R18)</t>
         </is>
       </c>
-      <c r="K176" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
+      <c r="K181" s="5" t="inlineStr">
+        <is>
+          <t>flag-off/env</t>
+        </is>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M176" s="4" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-019</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="M181" s="5" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>FD-CALC-024</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>Verify a discount on a line subtracts from the line total while a fee adds (fees add, discounts subtract in the line total)</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J177" s="4" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>API — Calculation contract</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Verify the backend per-line total includes the line's signed fee/discount amounts (Labor $250 + $50.00 + Part $20.00 + $2.20 → total_cost 322.20)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>SV-8480 (S3-R18)</t>
         </is>
       </c>
-      <c r="K177" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L177" s="4" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
         <is>
           <t>pending-create</t>
         </is>
       </c>
-      <c r="M177" s="4" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-020</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>Verify a line with no fees or discounts shows a line total of Labor + Parts only (unchanged by the fix)</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>SV-8480 (S3-R18)</t>
-        </is>
-      </c>
-      <c r="K178" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>pending-create</t>
-        </is>
-      </c>
-      <c r="M178" s="4" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-021</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>Verify the Estimate document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J179" s="4" t="inlineStr">
-        <is>
-          <t>SV-8480 (S3-R18)</t>
-        </is>
-      </c>
-      <c r="K179" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>pending-create</t>
-        </is>
-      </c>
-      <c r="M179" s="4" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-022</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>Verify the Invoice document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J180" s="4" t="inlineStr">
-        <is>
-          <t>SV-8480 (S3-R18)</t>
-        </is>
-      </c>
-      <c r="K180" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>pending-create</t>
-        </is>
-      </c>
-      <c r="M180" s="4" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-023</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>Verify that when the Fees &amp; Discounts feature is turned off, the line total is Labor + Parts only (gross), with no fee/discount rolled in</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G181" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H181" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>SV-8480 (S3-R18)</t>
-        </is>
-      </c>
-      <c r="K181" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L181" s="4" t="inlineStr">
-        <is>
-          <t>pending-create</t>
-        </is>
-      </c>
-      <c r="M181" s="4" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>FD-CALC-024</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>C (Calc/Perms/Validation)</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>API — Calculation contract</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>Verify the backend per-line total includes the line's signed fee/discount amounts (Labor $250 + $50.00 + Part $20.00 + $2.20 → total_cost 322.20)</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>SV-8480 (S3-R18)</t>
-        </is>
-      </c>
-      <c r="K182" s="4" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>pending-create</t>
-        </is>
-      </c>
-      <c r="M182" s="4" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" s="7" t="n"/>
     </row>
@@ -14312,7 +14312,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C22" s="7" t="n"/>
     </row>
@@ -14370,7 +14370,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="7" t="n"/>
     </row>
@@ -14396,7 +14396,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>unblocks the 19 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>unblocks the 6 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
+          <t>unblocks the 7 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>finalizes the 3 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 7 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 2 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 9 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -120,6 +120,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -127,9 +130,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -14930,7 +14930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -14948,228 +14948,230 @@
       <c r="C1" s="7" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="7" t="n"/>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Data as of:</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="C2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Total authored cases</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B4" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="C3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="n"/>
-      <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>— (ready to upload)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B8" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Dev fix / PO ruling / QA case-update</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>BLOCKED — DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Dev team (Stories 8 &amp; 11)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B10" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Dev / QA env (QuickBooks, flag-off)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>BLOCKED — NEEDS-ACCOUNT</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>QA (restricted-role session)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>QA (fresh cookies + seed data)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B13" s="8" t="n">
         <v>199</v>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>By authoring group</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-      <c r="C14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>A (WO/Parts)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>71</v>
       </c>
       <c r="C15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>B (Customer/Admin/Finance)</t>
+          <t>A (WO/Parts)</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>B (Customer/Admin/Finance)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="C17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B18" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>DEVIATION — by sub-bucket</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>PO-question</t>
+          <t>code-bug</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
@@ -15180,163 +15182,174 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
+          <t>PO-question</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B23" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>DEV NOT BUILT — by story</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>ENV — by sub-bucket</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-      <c r="C26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>quickbooks</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>14</v>
       </c>
       <c r="C27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>quickbooks</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B29" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
-        </is>
-      </c>
+      <c r="A30" s="7" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>• Fresh qb QA cookies (admin; tech quick-login is FLAKY — retest each run)</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="C32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>• Dev deploys Story 8 (Processing-Fee builder UI) + Story 11 (Part Sales fees/discounts)</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>unblocks the 0 DEV-NOT-BUILT cases (Story 8 = 0, Story 11 = 0); then QA re-runs VIU.</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="C33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>• A QuickBooks-connected env (or dev/QB-side inspection) for Story 6</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>unblocks the 14 QuickBooks ENV cases (mapping guard, sync, negative-total credit memo).</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="C34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>• A flag-off maintenance window on a non-shared env</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>unblocks the 7 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="C35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>• PO/dev rulings on the deviations + double-add + NOTE-FD-4</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>finalizes the 2 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 8 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="C36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>• Restricted-role accounts (or confirmation the self-service staff role-switch is usable on qb)</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>unblocks the 0 NEEDS-ACCOUNT Story-13 per-role negatives (restore Tech afterward).</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1456,72 +1456,72 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>FD-WO-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>The option is only hidden on the screen — the system still lets the change go through behind the scenes. Ask the team whether the system should also block it in the background, not just hide the button, then re-test.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner / Dev ruling</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>PO ruling — Whole-WO starting-places hidden without WO Create&amp;Edit is FE-only (BUG-FD-3). Same FE-vs-BE ruling as FD-PERM-002.</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>S1-N2 / S13-R3 / S13-N2 | SV-8479 (SV-8288 Story 12 — item 10)</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>PO-question</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>28436</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
@@ -2464,72 +2464,72 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>FD-PART-005</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Re-test on staging once a part can be moved from requested to received (this was blocked by an environment error before). Check the fee/discount stays attached after the part is received.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>§5-R13</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>reachable/needs-data</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>28450</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
         </is>
@@ -2896,72 +2896,72 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>FD-INLINE-003</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>A developer needs to add the 'Show N more' collapse so a line with two or more fees/discounts no longer shows them all at once. Re-test once fixed.</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>S3-R15 / S3-R16 / S12-R6</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>28456</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
@@ -3184,72 +3184,72 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>FD-STATS-002</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Verify each Stats fee/discount row names its target</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>A developer needs to change the Statistics tab to show one row per fee/discount that names its target. Re-test once that per-row layout is built.</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>S4-R3 / design §3</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>28460</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
@@ -3328,72 +3328,72 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>FD-STATS-004</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Once the Statistics tab shows one row per fee/discount, check they are listed oldest first. Re-test after the per-row layout is built by the developer.</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>§5-R9</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>28462</t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
@@ -4912,72 +4912,72 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>FD-WO-017</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>A developer needs to move the three-dot menu to the LEFT of 'Unassigned' (it currently sits on the right); the label is already correct. Re-test the left placement once the fix is in.</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement, three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
         </is>
       </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>30618</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr">
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
         </is>
@@ -5992,144 +5992,144 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>FD-CUST-005</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>Re-check on staging how a Processing Fee template's type is shown in the customer picker, and confirm with the team whether showing it as 'Fee' is acceptable or needs fixing.</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K77" s="3" t="inlineStr">
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
         </is>
       </c>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="L77" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr">
+      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>28489</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr">
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>FD-CUST-006</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>Accepted as-is by the team — the picker shows 'No results' when there is nothing left to add. Update the test case wording to expect 'No results'; no developer fix needed.</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K78" s="3" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>S9-R22</t>
         </is>
       </c>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>28490</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
@@ -7504,72 +7504,72 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>FD-TMPL-010</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>The line-level dialog currently has no 'Apply From Template' picker, so template scoping can't be checked there. Re-check on staging whether that picker now exists; if it is still missing, confirm with the team whether that is intended.</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K98" s="3" t="inlineStr">
+      <c r="K98" s="4" t="inlineStr">
         <is>
           <t>S2-R14, S2-R15, S2-R16, S5-R10 | SV-8479 (SV-8288 Story 12 — items 1 &amp; 2 label sweep)</t>
         </is>
       </c>
-      <c r="L98" s="3" t="inlineStr">
+      <c r="L98" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M98" s="3" t="inlineStr">
+      <c r="M98" s="4" t="inlineStr">
         <is>
           <t>28511</t>
         </is>
       </c>
-      <c r="N98" s="3" t="inlineStr">
+      <c r="N98" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
@@ -8584,144 +8584,144 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>FD-PROC-008</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>The menu still offers an 'Edit' option for a Processing Fee even though editing does nothing (only 'Remove' works). A developer needs to make it remove-only. Re-test once fixed.</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="I113" s="4" t="inlineStr">
         <is>
           <t>QA (case-text update)</t>
         </is>
       </c>
-      <c r="J113" s="3" t="inlineStr">
+      <c r="J113" s="4" t="inlineStr">
         <is>
           <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
         </is>
       </c>
-      <c r="K113" s="3" t="inlineStr">
+      <c r="K113" s="4" t="inlineStr">
         <is>
           <t>S8-R17, S8-N5, S3-R9</t>
         </is>
       </c>
-      <c r="L113" s="3" t="inlineStr">
+      <c r="L113" s="4" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="M113" s="3" t="inlineStr">
+      <c r="M113" s="4" t="inlineStr">
         <is>
           <t>28526</t>
         </is>
       </c>
-      <c r="N113" s="3" t="inlineStr">
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>FD-PROC-009</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>A developer needs to fix the Processing Fee amount — its base should NOT include the whole-work-order fees/discounts (or their tax). Re-test the amount once fixed.</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G114" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H114" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="I114" s="4" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
-      <c r="J114" s="3" t="inlineStr">
+      <c r="J114" s="4" t="inlineStr">
         <is>
           <t>Dev fix — FDBUG-2 — processing-fee Grand-Total base wrongly includes whole-WO fees + their tax.</t>
         </is>
       </c>
-      <c r="K114" s="3" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
         </is>
       </c>
-      <c r="L114" s="3" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr">
         <is>
           <t>code-bug</t>
         </is>
       </c>
-      <c r="M114" s="3" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
         <is>
           <t>28527</t>
         </is>
       </c>
-      <c r="N114" s="3" t="inlineStr">
+      <c r="N114" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
@@ -12544,72 +12544,72 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>FD-CALC-013</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="C168" s="4" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="D168" s="4" t="inlineStr">
         <is>
           <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
         <is>
           <t>VIU-Deviation</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr">
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>Same Processing Fee amount problem — the base wrongly includes the whole-work-order fees/discounts. A developer needs to fix it; re-test the amount once fixed.</t>
         </is>
       </c>
-      <c r="G168" s="3" t="inlineStr">
+      <c r="G168" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
+      <c r="H168" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="I168" s="3" t="inlineStr">
+      <c r="I168" s="4" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
-      <c r="J168" s="3" t="inlineStr">
+      <c r="J168" s="4" t="inlineStr">
         <is>
           <t>Dev fix — FDBUG-2 — processing-fee base includes whole-WO adjustments.</t>
         </is>
       </c>
-      <c r="K168" s="3" t="inlineStr">
+      <c r="K168" s="4" t="inlineStr">
         <is>
           <t>§5-R4, §5-R5</t>
         </is>
       </c>
-      <c r="L168" s="3" t="inlineStr">
+      <c r="L168" s="4" t="inlineStr">
         <is>
           <t>code-bug</t>
         </is>
       </c>
-      <c r="M168" s="3" t="inlineStr">
+      <c r="M168" s="4" t="inlineStr">
         <is>
           <t>28580</t>
         </is>
       </c>
-      <c r="N168" s="3" t="inlineStr">
+      <c r="N168" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
@@ -13480,72 +13480,72 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>FD-PERM-002</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D181" s="3" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>The system only hides the option on the screen — it still allows the change in the background. Ask the team whether the system should also block it in the background, then re-test.</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I181" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner / Dev ruling</t>
-        </is>
-      </c>
-      <c r="J181" s="3" t="inlineStr">
-        <is>
-          <t>PO ruling — Whole-WO adjustment add/edit/remove is FE-only at the BE (tech got 201) (BUG-FD-3). PO/dev: should whole-WO writes be BE-enforced for V1?</t>
-        </is>
-      </c>
-      <c r="K181" s="3" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
         <is>
           <t>S13-R3</t>
         </is>
       </c>
-      <c r="L181" s="3" t="inlineStr">
-        <is>
-          <t>PO-question</t>
-        </is>
-      </c>
-      <c r="M181" s="3" t="inlineStr">
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
         <is>
           <t>28586</t>
         </is>
       </c>
-      <c r="N181" s="3" t="inlineStr">
+      <c r="N181" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -15014,15 +15014,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Dev fix / PO ruling / QA case-update</t>
         </is>
@@ -15074,15 +15074,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>QA (fresh cookies + seed data)</t>
         </is>
@@ -15186,7 +15186,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22" s="7" t="n"/>
     </row>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>finalizes the 2 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 8 copy/UX-drift deviations once the build is confirmed intended.</t>
+          <t>finalizes the 0 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 8 copy/UX-drift deviations once the build is confirmed intended.</t>
         </is>
       </c>
       <c r="C36" s="7" t="n"/>

--- a/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
+++ b/build/fees-discounts/FeesDiscounts_Blockers_Tracker.xlsx
@@ -61,17 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2D9F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,12 +108,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -124,6 +118,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2464,72 +2464,72 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>FD-PART-005</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Re-test on staging once a part can be moved from requested to received (this was blocked by an environment error before). Check the fee/discount stays attached after the part is received.</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Fresh qb cookies + seeded/throwaway data; drive this built surface (parts UI flows, invoice-time walk, misc retests — see viu-qb-findings.md batch-2 backlog).</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>§5-R13</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>reachable/needs-data</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>28450</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
         </is>
@@ -2896,72 +2896,72 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>FD-INLINE-003</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>A developer needs to add the 'Show N more' collapse so a line with two or more fees/discounts no longer shows them all at once. Re-test once fixed.</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>S3-R15 / S3-R16 / S12-R6</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>28456</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
@@ -3184,72 +3184,72 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FD-STATS-002</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Verify each Stats fee/discount row names its target</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>A developer needs to change the Statistics tab to show one row per fee/discount that names its target. Re-test once that per-row layout is built.</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>S4-R3 / design §3</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Statistics tab lists each fee/discount as its own row with name, percent and amount</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SV-8280 (§3 adjustments appear on the Statistics tab; §5-R9 oldest-first)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>28460</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
@@ -3328,72 +3328,72 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>FD-STATS-004</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Work Order — Statistics tab</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Once the Statistics tab shows one row per fee/discount, check they are listed oldest first. Re-test after the per-row layout is built by the developer.</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>§5-R9</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>28462</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
@@ -4912,72 +4912,72 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>FD-WO-017</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>A developer needs to move the three-dot menu to the LEFT of 'Unassigned' (it currently sits on the right); the label is already correct. Re-test the left placement once the fix is in.</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement, three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the RIGHT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement,three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>30618</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
         </is>
@@ -5992,144 +5992,144 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>FD-CUST-005</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Re-check on staging how a Processing Fee template's type is shown in the customer picker, and confirm with the team whether showing it as 'Fee' is acceptable or needs fixing.</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M77" s="4" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SV-8284,SV-8285 (S9-R19,S8-R15,S9-R... (Processing Fee shows as "Fee"))</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>28489</t>
         </is>
       </c>
-      <c r="N77" s="4" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>FD-CUST-006</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Accepted as-is by the team — the picker shows 'No results' when there is nothing left to add. Update the test case wording to expect 'No results'; no developer fix needed.</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>S9-R22</t>
         </is>
       </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>28490</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
@@ -7504,72 +7504,72 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>FD-TMPL-010</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>The line-level dialog currently has no 'Apply From Template' picker, so template scoping can't be checked there. Re-check on staging whether that picker now exists; if it is still missing, confirm with the team whether that is intended.</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K98" s="4" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>S2-R14, S2-R15, S2-R16, S5-R10 | SV-8479 (SV-8288 Story 12 — items 1 &amp; 2 label sweep)</t>
         </is>
       </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M98" s="4" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>28511</t>
         </is>
       </c>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
@@ -7648,72 +7648,72 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>FD-TMPL-012</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>Needs an environment where the template library can be emptied (the shared one always has templates). Test the empty-state message when that is available.</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" s="3" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>Environment window — shared env: cannot empty the location's template library (real templates in use).</t>
         </is>
       </c>
-      <c r="K100" s="5" t="inlineStr">
+      <c r="K100" s="3" t="inlineStr">
         <is>
           <t>S7-R11</t>
         </is>
       </c>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="M100" s="5" t="inlineStr">
+      <c r="M100" s="3" t="inlineStr">
         <is>
           <t>28513</t>
         </is>
       </c>
-      <c r="N100" s="5" t="inlineStr">
+      <c r="N100" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28513</t>
         </is>
@@ -8584,144 +8584,144 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>FD-PROC-008</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>The menu still offers an 'Edit' option for a Processing Fee even though editing does nothing (only 'Remove' works). A developer needs to make it remove-only. Re-test once fixed.</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>QA (case-text update)</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>Build deviates from spec wording/UX — update case text once the build is confirmed intended (label/copy/UX drift; see viu-qb-findings.md).</t>
-        </is>
-      </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>S8-R17, S8-N5, S3-R9</t>
-        </is>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>case-update</t>
-        </is>
-      </c>
-      <c r="M113" s="4" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>SV-8279,SV-8284 (S8-R17,S8-N5,S3-R9)</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
         <is>
           <t>28526</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>FD-PROC-009</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>A developer needs to fix the Processing Fee amount — its base should NOT include the whole-work-order fees/discounts (or their tax). Re-test the amount once fixed.</t>
-        </is>
-      </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-2 — processing-fee Grand-Total base wrongly includes whole-WO fees + their tax.</t>
-        </is>
-      </c>
-      <c r="K114" s="4" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
         </is>
       </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="M114" s="4" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>28527</t>
         </is>
       </c>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
@@ -9880,792 +9880,792 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>FD-QB-001</t>
         </is>
       </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G131" s="5" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="H131" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="I131" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J131" s="5" t="inlineStr">
+      <c r="J131" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K131" s="5" t="inlineStr">
+      <c r="K131" s="3" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
       </c>
-      <c r="L131" s="5" t="inlineStr">
+      <c r="L131" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M131" s="5" t="inlineStr">
+      <c r="M131" s="3" t="inlineStr">
         <is>
           <t>28544</t>
         </is>
       </c>
-      <c r="N131" s="5" t="inlineStr">
+      <c r="N131" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28544</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>FD-QB-002</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="H132" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I132" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J132" s="5" t="inlineStr">
+      <c r="J132" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K132" s="5" t="inlineStr">
+      <c r="K132" s="3" t="inlineStr">
         <is>
           <t>S6-R3, S6-R5</t>
         </is>
       </c>
-      <c r="L132" s="5" t="inlineStr">
+      <c r="L132" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M132" s="5" t="inlineStr">
+      <c r="M132" s="3" t="inlineStr">
         <is>
           <t>28545</t>
         </is>
       </c>
-      <c r="N132" s="5" t="inlineStr">
+      <c r="N132" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28545</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>FD-QB-003</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>QuickBooks sync — edge</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G133" s="5" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J133" s="5" t="inlineStr">
+      <c r="J133" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K133" s="5" t="inlineStr">
+      <c r="K133" s="3" t="inlineStr">
         <is>
           <t>S6-R1, §5-R8</t>
         </is>
       </c>
-      <c r="L133" s="5" t="inlineStr">
+      <c r="L133" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M133" s="5" t="inlineStr">
+      <c r="M133" s="3" t="inlineStr">
         <is>
           <t>28546</t>
         </is>
       </c>
-      <c r="N133" s="5" t="inlineStr">
+      <c r="N133" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28546</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>FD-QB-004</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J134" s="5" t="inlineStr">
+      <c r="J134" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K134" s="5" t="inlineStr">
+      <c r="K134" s="3" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6a, S6-R6d</t>
         </is>
       </c>
-      <c r="L134" s="5" t="inlineStr">
+      <c r="L134" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M134" s="5" t="inlineStr">
+      <c r="M134" s="3" t="inlineStr">
         <is>
           <t>28547</t>
         </is>
       </c>
-      <c r="N134" s="5" t="inlineStr">
+      <c r="N134" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28547</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>FD-QB-005</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="E135" s="5" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G135" s="5" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J135" s="5" t="inlineStr">
+      <c r="J135" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K135" s="5" t="inlineStr">
+      <c r="K135" s="3" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6d</t>
         </is>
       </c>
-      <c r="L135" s="5" t="inlineStr">
+      <c r="L135" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M135" s="5" t="inlineStr">
+      <c r="M135" s="3" t="inlineStr">
         <is>
           <t>28548</t>
         </is>
       </c>
-      <c r="N135" s="5" t="inlineStr">
+      <c r="N135" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28548</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>FD-QB-006</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H136" s="5" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J136" s="5" t="inlineStr">
+      <c r="J136" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K136" s="5" t="inlineStr">
+      <c r="K136" s="3" t="inlineStr">
         <is>
           <t>S6-R6a</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr">
+      <c r="L136" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M136" s="5" t="inlineStr">
+      <c r="M136" s="3" t="inlineStr">
         <is>
           <t>28549</t>
         </is>
       </c>
-      <c r="N136" s="5" t="inlineStr">
+      <c r="N136" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28549</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>FD-QB-007</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G137" s="5" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H137" s="5" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I137" s="5" t="inlineStr">
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J137" s="5" t="inlineStr">
+      <c r="J137" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K137" s="5" t="inlineStr">
+      <c r="K137" s="3" t="inlineStr">
         <is>
           <t>S6-R6b</t>
         </is>
       </c>
-      <c r="L137" s="5" t="inlineStr">
+      <c r="L137" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M137" s="5" t="inlineStr">
+      <c r="M137" s="3" t="inlineStr">
         <is>
           <t>28550</t>
         </is>
       </c>
-      <c r="N137" s="5" t="inlineStr">
+      <c r="N137" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28550</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>FD-QB-008</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F138" s="5" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G138" s="5" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H138" s="5" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I138" s="5" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J138" s="5" t="inlineStr">
+      <c r="J138" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K138" s="5" t="inlineStr">
+      <c r="K138" s="3" t="inlineStr">
         <is>
           <t>S6-R6c</t>
         </is>
       </c>
-      <c r="L138" s="5" t="inlineStr">
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M138" s="5" t="inlineStr">
+      <c r="M138" s="3" t="inlineStr">
         <is>
           <t>28551</t>
         </is>
       </c>
-      <c r="N138" s="5" t="inlineStr">
+      <c r="N138" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28551</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>FD-QB-009</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company; the unmap action also currently errors on this environment. Test once QuickBooks is connected and that is working.</t>
         </is>
       </c>
-      <c r="G139" s="5" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H139" s="5" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I139" s="5" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr">
+      <c r="J139" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K139" s="5" t="inlineStr">
+      <c r="K139" s="3" t="inlineStr">
         <is>
           <t>S6-R7, S6-R7a</t>
         </is>
       </c>
-      <c r="L139" s="5" t="inlineStr">
+      <c r="L139" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M139" s="5" t="inlineStr">
+      <c r="M139" s="3" t="inlineStr">
         <is>
           <t>28552</t>
         </is>
       </c>
-      <c r="N139" s="5" t="inlineStr">
+      <c r="N139" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28552</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>FD-QB-010</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — Class</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G140" s="5" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H140" s="5" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I140" s="5" t="inlineStr">
+      <c r="I140" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J140" s="5" t="inlineStr">
+      <c r="J140" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K140" s="5" t="inlineStr">
+      <c r="K140" s="3" t="inlineStr">
         <is>
           <t>S6-R8</t>
         </is>
       </c>
-      <c r="L140" s="5" t="inlineStr">
+      <c r="L140" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M140" s="5" t="inlineStr">
+      <c r="M140" s="3" t="inlineStr">
         <is>
           <t>28553</t>
         </is>
       </c>
-      <c r="N140" s="5" t="inlineStr">
+      <c r="N140" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28553</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>FD-QB-011</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — Class validation</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H141" s="5" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I141" s="5" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J141" s="5" t="inlineStr">
+      <c r="J141" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K141" s="5" t="inlineStr">
+      <c r="K141" s="3" t="inlineStr">
         <is>
           <t>S6-R9</t>
         </is>
       </c>
-      <c r="L141" s="5" t="inlineStr">
+      <c r="L141" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M141" s="5" t="inlineStr">
+      <c r="M141" s="3" t="inlineStr">
         <is>
           <t>28554</t>
         </is>
       </c>
-      <c r="N141" s="5" t="inlineStr">
+      <c r="N141" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28554</t>
         </is>
@@ -10744,72 +10744,72 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>FD-QB-013</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G143" s="5" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H143" s="5" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I143" s="5" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J143" s="5" t="inlineStr">
+      <c r="J143" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K143" s="5" t="inlineStr">
+      <c r="K143" s="3" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="L143" s="5" t="inlineStr">
+      <c r="L143" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M143" s="5" t="inlineStr">
+      <c r="M143" s="3" t="inlineStr">
         <is>
           <t>28556</t>
         </is>
       </c>
-      <c r="N143" s="5" t="inlineStr">
+      <c r="N143" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28556</t>
         </is>
@@ -10888,144 +10888,144 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>FD-QB-015</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
-      <c r="E145" s="5" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G145" s="5" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H145" s="5" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I145" s="5" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J145" s="5" t="inlineStr">
+      <c r="J145" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K145" s="5" t="inlineStr">
+      <c r="K145" s="3" t="inlineStr">
         <is>
           <t>S6-R11, S6-R13</t>
         </is>
       </c>
-      <c r="L145" s="5" t="inlineStr">
+      <c r="L145" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M145" s="5" t="inlineStr">
+      <c r="M145" s="3" t="inlineStr">
         <is>
           <t>28558</t>
         </is>
       </c>
-      <c r="N145" s="5" t="inlineStr">
+      <c r="N145" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28558</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>FD-QB-016</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>QuickBooks sync — tax</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
         </is>
       </c>
-      <c r="E146" s="5" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
         </is>
       </c>
-      <c r="G146" s="5" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H146" s="5" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I146" s="5" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env</t>
         </is>
       </c>
-      <c r="J146" s="5" t="inlineStr">
+      <c r="J146" s="3" t="inlineStr">
         <is>
           <t>QuickBooks integration not present on qb env (Story 6). Needs a QB-connected env or dev/QB-side inspection.</t>
         </is>
       </c>
-      <c r="K146" s="5" t="inlineStr">
+      <c r="K146" s="3" t="inlineStr">
         <is>
           <t>S6-R2, §5-R11</t>
         </is>
       </c>
-      <c r="L146" s="5" t="inlineStr">
+      <c r="L146" s="3" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="M146" s="5" t="inlineStr">
+      <c r="M146" s="3" t="inlineStr">
         <is>
           <t>28559</t>
         </is>
       </c>
-      <c r="N146" s="5" t="inlineStr">
+      <c r="N146" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28559</t>
         </is>
@@ -11248,72 +11248,72 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>FD-HIST-004</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>Audit log — visibility</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>Needs a window where the Fees &amp; Discounts feature can be turned off (it can't be toggled on the shared environment). Test when that is available.</t>
         </is>
       </c>
-      <c r="G150" s="5" t="inlineStr">
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H150" s="5" t="inlineStr">
+      <c r="H150" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I150" s="5" t="inlineStr">
+      <c r="I150" s="3" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="J150" s="5" t="inlineStr">
+      <c r="J150" s="3" t="inlineStr">
         <is>
           <t>Environment window — flag-off history visibility (org flag toggle skipped on shared env).</t>
         </is>
       </c>
-      <c r="K150" s="5" t="inlineStr">
+      <c r="K150" s="3" t="inlineStr">
         <is>
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="L150" s="5" t="inlineStr">
+      <c r="L150" s="3" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="M150" s="5" t="inlineStr">
+      <c r="M150" s="3" t="inlineStr">
         <is>
           <t>28563</t>
         </is>
       </c>
-      <c r="N150" s="5" t="inlineStr">
+      <c r="N150" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28563</t>
         </is>
@@ -12544,72 +12544,72 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="4" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>FD-CALC-013</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C168" s="4" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>Same Processing Fee amount problem — the base wrongly includes the whole-work-order fees/discounts. A developer needs to fix it; re-test the amount once fixed.</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — DEVIATION</t>
-        </is>
-      </c>
-      <c r="I168" s="4" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>Dev fix — FDBUG-2 — processing-fee base includes whole-WO adjustments.</t>
-        </is>
-      </c>
-      <c r="K168" s="4" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
         <is>
           <t>§5-R4, §5-R5</t>
         </is>
       </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>code-bug</t>
-        </is>
-      </c>
-      <c r="M168" s="4" t="inlineStr">
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
         <is>
           <t>28580</t>
         </is>
       </c>
-      <c r="N168" s="4" t="inlineStr">
+      <c r="N168" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
@@ -12832,72 +12832,72 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>FD-CALC-017</t>
         </is>
       </c>
-      <c r="B172" s="5" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
         </is>
       </c>
-      <c r="E172" s="5" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F172" s="5" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>Needs a QuickBooks-connected company to check the penny-rounding on discount lines. Test once QuickBooks is connected.</t>
         </is>
       </c>
-      <c r="G172" s="5" t="inlineStr">
+      <c r="G172" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H172" s="5" t="inlineStr">
+      <c r="H172" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I172" s="5" t="inlineStr">
+      <c r="I172" s="3" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="J172" s="5" t="inlineStr">
+      <c r="J172" s="3" t="inlineStr">
         <is>
           <t>Environment window — environment limitation on the shared qb env.</t>
         </is>
       </c>
-      <c r="K172" s="5" t="inlineStr">
+      <c r="K172" s="3" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="L172" s="5" t="inlineStr">
+      <c r="L172" s="3" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="M172" s="5" t="inlineStr">
+      <c r="M172" s="3" t="inlineStr">
         <is>
           <t>28584</t>
         </is>
       </c>
-      <c r="N172" s="5" t="inlineStr">
+      <c r="N172" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28584</t>
         </is>
@@ -13264,72 +13264,72 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>FD-CALC-023</t>
         </is>
       </c>
-      <c r="B178" s="5" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C178" s="5" t="inlineStr">
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Verify that when the Fees &amp; Discounts feature is turned off, the line total is Labor + Parts only (gross), with no fee/discount rolled in</t>
         </is>
       </c>
-      <c r="E178" s="5" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F178" s="5" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>Needs an environment with the Fees &amp; Discounts feature turned OFF (it can't be toggled on the shared one). Test when that is available.</t>
         </is>
       </c>
-      <c r="G178" s="5" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H178" s="5" t="inlineStr">
+      <c r="H178" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I178" s="5" t="inlineStr">
+      <c r="I178" s="3" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="J178" s="5" t="inlineStr">
+      <c r="J178" s="3" t="inlineStr">
         <is>
           <t>Environment window — environment limitation on the shared qb env.</t>
         </is>
       </c>
-      <c r="K178" s="5" t="inlineStr">
+      <c r="K178" s="3" t="inlineStr">
         <is>
           <t>SV-8480 (S3-R18)</t>
         </is>
       </c>
-      <c r="L178" s="5" t="inlineStr">
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="M178" s="5" t="inlineStr">
+      <c r="M178" s="3" t="inlineStr">
         <is>
           <t>30634</t>
         </is>
       </c>
-      <c r="N178" s="5" t="inlineStr">
+      <c r="N178" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30634</t>
         </is>
@@ -14200,216 +14200,216 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="inlineStr">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t>FD-FLAG-001</t>
         </is>
       </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
-      <c r="E191" s="5" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
         <is>
           <t>Needs a window where the Fees &amp; Discounts feature can be turned off. Test when that is available.</t>
         </is>
       </c>
-      <c r="G191" s="5" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H191" s="5" t="inlineStr">
+      <c r="H191" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I191" s="5" t="inlineStr">
+      <c r="I191" s="3" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="J191" s="5" t="inlineStr">
+      <c r="J191" s="3" t="inlineStr">
         <is>
           <t>Environment window — flag-off window (org-level FeesAndDiscounts toggle skipped on shared env).</t>
         </is>
       </c>
-      <c r="K191" s="5" t="inlineStr">
+      <c r="K191" s="3" t="inlineStr">
         <is>
           <t>§1 feature flag, S13-R1</t>
         </is>
       </c>
-      <c r="L191" s="5" t="inlineStr">
+      <c r="L191" s="3" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="M191" s="5" t="inlineStr">
+      <c r="M191" s="3" t="inlineStr">
         <is>
           <t>28596</t>
         </is>
       </c>
-      <c r="N191" s="5" t="inlineStr">
+      <c r="N191" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28596</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="inlineStr">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>FD-FLAG-002</t>
         </is>
       </c>
-      <c r="B192" s="5" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C192" s="5" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
-      <c r="E192" s="5" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F192" s="5" t="inlineStr">
+      <c r="F192" s="3" t="inlineStr">
         <is>
           <t>Needs a window where the Fees &amp; Discounts feature can be turned off. Test when that is available.</t>
         </is>
       </c>
-      <c r="G192" s="5" t="inlineStr">
+      <c r="G192" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H192" s="5" t="inlineStr">
+      <c r="H192" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I192" s="5" t="inlineStr">
+      <c r="I192" s="3" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="J192" s="5" t="inlineStr">
+      <c r="J192" s="3" t="inlineStr">
         <is>
           <t>Environment window — flag-off exception (history log visible with flag off).</t>
         </is>
       </c>
-      <c r="K192" s="5" t="inlineStr">
+      <c r="K192" s="3" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="L192" s="5" t="inlineStr">
+      <c r="L192" s="3" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="M192" s="5" t="inlineStr">
+      <c r="M192" s="3" t="inlineStr">
         <is>
           <t>28597</t>
         </is>
       </c>
-      <c r="N192" s="5" t="inlineStr">
+      <c r="N192" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28597</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="inlineStr">
+      <c r="A193" s="3" t="inlineStr">
         <is>
           <t>FD-FLAG-003</t>
         </is>
       </c>
-      <c r="B193" s="5" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="C193" s="5" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
-      <c r="E193" s="5" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>VIU-Blocked-Env</t>
         </is>
       </c>
-      <c r="F193" s="5" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
         <is>
           <t>Needs a window where the Fees &amp; Discounts feature can be turned off. Test when that is available.</t>
         </is>
       </c>
-      <c r="G193" s="5" t="inlineStr">
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="H193" s="5" t="inlineStr">
+      <c r="H193" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="I193" s="5" t="inlineStr">
+      <c r="I193" s="3" t="inlineStr">
         <is>
           <t>QA env</t>
         </is>
       </c>
-      <c r="J193" s="5" t="inlineStr">
+      <c r="J193" s="3" t="inlineStr">
         <is>
           <t>Environment window — flag ON + permission-required interaction (flag-side complement).</t>
         </is>
       </c>
-      <c r="K193" s="5" t="inlineStr">
+      <c r="K193" s="3" t="inlineStr">
         <is>
           <t>§1 feature flag + S13-R1</t>
         </is>
       </c>
-      <c r="L193" s="5" t="inlineStr">
+      <c r="L193" s="3" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="M193" s="5" t="inlineStr">
+      <c r="M193" s="3" t="inlineStr">
         <is>
           <t>28598</t>
         </is>
       </c>
-      <c r="N193" s="5" t="inlineStr">
+      <c r="N193" s="3" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28598</t>
         </is>
@@ -14939,60 +14939,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Fees &amp; Discounts V1 — Blockers Tracker · Summary</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
-      <c r="C1" s="7" t="n"/>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Data as of:</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n"/>
+      <c r="C2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Total authored cases</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="5" t="n">
         <v>199</v>
       </c>
-      <c r="C4" s="7" t="n"/>
+      <c r="C4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -15014,255 +15014,255 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>BLOCKED — DEVIATION</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Dev fix / PO ruling / QA case-update</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>BLOCKED — DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Dev team (Stories 8 &amp; 11)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>BLOCKED — ENV</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Dev / QA env (QuickBooks, flag-off)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>BLOCKED — NEEDS-ACCOUNT</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>QA (restricted-role session)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>BLOCKED — VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>QA (fresh cookies + seed data)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="6" t="n">
         <v>199</v>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>By authoring group</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n"/>
+      <c r="C15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>A (WO/Parts)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="C16" s="7" t="n"/>
+      <c r="C16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>B (Customer/Admin/Finance)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="C17" s="7" t="n"/>
+      <c r="C17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>C (Calc/Perms/Validation)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="C18" s="7" t="n"/>
+      <c r="C18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>DEVIATION — by sub-bucket</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
+      <c r="C20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>code-bug</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="7" t="n"/>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>PO-question</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="7" t="n"/>
+      <c r="C22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>case-update</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7" t="n"/>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>DEV NOT BUILT — by story</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
+      <c r="C25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>ENV — by sub-bucket</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
+      <c r="C27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>quickbooks</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C28" s="7" t="n"/>
+      <c r="C28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>flag-off/env</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C29" s="7" t="n"/>
+      <c r="C29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -15270,86 +15270,86 @@
           <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>• Fresh qb QA cookies (admin; tech quick-login is FLAKY — retest each run)</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>unblocks the 1 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>unblocks the 0 VIU-PENDING cases (parts UI flows, invoice-time walk, retests) AND — via the self-service staff role-switch — the 0 NEEDS-ACCOUNT Story-13 per-role negatives.</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>• Dev deploys Story 8 (Processing-Fee builder UI) + Story 11 (Part Sales fees/discounts)</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>unblocks the 0 DEV-NOT-BUILT cases (Story 8 = 0, Story 11 = 0); then QA re-runs VIU.</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
+      <c r="C33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>• A QuickBooks-connected env (or dev/QB-side inspection) for Story 6</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>unblocks the 14 QuickBooks ENV cases (mapping guard, sync, negative-total credit memo).</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
+      <c r="C34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>• A flag-off maintenance window on a non-shared env</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>unblocks the 7 flag-off/shared-env cases (FD-FLAG-001/002/003, FD-HIST-004, FD-TMPL-012).</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n"/>
+      <c r="C35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>• PO/dev rulings on the deviations + double-add + NOTE-FD-4</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>finalizes the 0 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 2 code-bug deviations; QA updates the 8 copy/UX-drift deviations once the build is confirmed intended.</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>finalizes the 0 PO-question deviations (Stats layout, whole-WO FE-vs-BE enforcement), the double-add confirmation (FD-VAL-007; the duplicate FD-CUST-016/C28500 was retired 2026-07-20), and NOTE-FD-4 (BE accepts processing_fee). Dev fixes finalize the 0 code-bug deviations; QA updates the 0 copy/UX-drift deviations once the build is confirmed intended.</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>• Restricted-role accounts (or confirmation the self-service staff role-switch is usable on qb)</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>unblocks the 0 NEEDS-ACCOUNT Story-13 per-role negatives (restore Tech afterward).</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n"/>
+      <c r="C37" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
